--- a/research/traditional_assets/database/data/bulgaria/bulgaria_farming_agriculture.xlsx
+++ b/research/traditional_assets/database/data/bulgaria/bulgaria_farming_agriculture.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08385587254441154</v>
+        <v>0.08381251667186712</v>
       </c>
       <c r="C2">
-        <v>37.11422857471901</v>
+        <v>36.78572649857228</v>
       </c>
       <c r="D2">
-        <v>32.72422857471901</v>
+        <v>32.73772649857228</v>
       </c>
       <c r="E2">
-        <v>-21.1</v>
+        <v>-20.758</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.342</v>
       </c>
       <c r="G2">
         <v>4.39</v>
@@ -1445,28 +1445,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0172026</v>
       </c>
       <c r="N2">
-        <v>4.066666666666667</v>
+        <v>4.049464066666667</v>
       </c>
       <c r="O2">
-        <v>0.4066666666666667</v>
+        <v>0.4049464066666668</v>
       </c>
       <c r="P2">
-        <v>3.660000000000001</v>
+        <v>3.64451766</v>
       </c>
       <c r="Q2">
-        <v>6.960000000000001</v>
+        <v>6.944517660000001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08385587254441154</v>
+        <v>0.084201835022088</v>
       </c>
       <c r="T2">
-        <v>0.5887122450442503</v>
+        <v>0.5940641745446525</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>236.3983738892183</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08381251667186712</v>
+        <v>0.08376916079932273</v>
       </c>
       <c r="C3">
-        <v>36.78572649857228</v>
+        <v>36.45723556213074</v>
       </c>
       <c r="D3">
-        <v>32.73772649857228</v>
+        <v>32.75123556213074</v>
       </c>
       <c r="E3">
-        <v>-20.758</v>
+        <v>-20.416</v>
       </c>
       <c r="F3">
-        <v>0.342</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="G3">
         <v>4.39</v>
@@ -1527,28 +1527,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M3">
-        <v>0.0172026</v>
+        <v>0.0344052</v>
       </c>
       <c r="N3">
-        <v>4.049464066666667</v>
+        <v>4.032261466666667</v>
       </c>
       <c r="O3">
-        <v>0.4049464066666668</v>
+        <v>0.4032261466666667</v>
       </c>
       <c r="P3">
-        <v>3.64451766</v>
+        <v>3.62903532</v>
       </c>
       <c r="Q3">
-        <v>6.944517660000001</v>
+        <v>6.929035320000001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.084201835022088</v>
+        <v>0.08455485795849257</v>
       </c>
       <c r="T3">
-        <v>0.5940641745446525</v>
+        <v>0.5995253270960835</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>236.3983738892183</v>
+        <v>118.1991869446092</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08376916079932273</v>
+        <v>0.08372580492677829</v>
       </c>
       <c r="C4">
-        <v>36.45723556213074</v>
+        <v>36.12875577919036</v>
       </c>
       <c r="D4">
-        <v>32.75123556213074</v>
+        <v>32.76475577919037</v>
       </c>
       <c r="E4">
-        <v>-20.416</v>
+        <v>-20.074</v>
       </c>
       <c r="F4">
-        <v>0.6840000000000001</v>
+        <v>1.026</v>
       </c>
       <c r="G4">
         <v>4.39</v>
@@ -1609,28 +1609,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M4">
-        <v>0.0344052</v>
+        <v>0.0516078</v>
       </c>
       <c r="N4">
-        <v>4.032261466666667</v>
+        <v>4.015058866666667</v>
       </c>
       <c r="O4">
-        <v>0.4032261466666667</v>
+        <v>0.4015058866666668</v>
       </c>
       <c r="P4">
-        <v>3.62903532</v>
+        <v>3.613552980000001</v>
       </c>
       <c r="Q4">
-        <v>6.929035320000001</v>
+        <v>6.91355298</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08455485795849257</v>
+        <v>0.08491515971832814</v>
       </c>
       <c r="T4">
-        <v>0.5995253270960835</v>
+        <v>0.605099080731049</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>118.1991869446092</v>
+        <v>78.79945796307278</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08372580492677829</v>
+        <v>0.0836824490542339</v>
       </c>
       <c r="C5">
-        <v>36.12875577919036</v>
+        <v>35.80028716356983</v>
       </c>
       <c r="D5">
-        <v>32.76475577919037</v>
+        <v>32.77828716356984</v>
       </c>
       <c r="E5">
-        <v>-20.074</v>
+        <v>-19.732</v>
       </c>
       <c r="F5">
-        <v>1.026</v>
+        <v>1.368</v>
       </c>
       <c r="G5">
         <v>4.39</v>
@@ -1691,28 +1691,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M5">
-        <v>0.0516078</v>
+        <v>0.06881040000000001</v>
       </c>
       <c r="N5">
-        <v>4.015058866666667</v>
+        <v>3.997856266666667</v>
       </c>
       <c r="O5">
-        <v>0.4015058866666668</v>
+        <v>0.3997856266666668</v>
       </c>
       <c r="P5">
-        <v>3.613552980000001</v>
+        <v>3.598070640000001</v>
       </c>
       <c r="Q5">
-        <v>6.91355298</v>
+        <v>6.89807064</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08491515971832814</v>
+        <v>0.08528296776482698</v>
       </c>
       <c r="T5">
-        <v>0.605099080731049</v>
+        <v>0.6107889542334098</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>78.79945796307278</v>
+        <v>59.09959347230458</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0836824490542339</v>
+        <v>0.08363909318168948</v>
       </c>
       <c r="C6">
-        <v>35.80028716356983</v>
+        <v>35.47182972911072</v>
       </c>
       <c r="D6">
-        <v>32.77828716356984</v>
+        <v>32.79182972911072</v>
       </c>
       <c r="E6">
-        <v>-19.732</v>
+        <v>-19.39</v>
       </c>
       <c r="F6">
-        <v>1.368</v>
+        <v>1.71</v>
       </c>
       <c r="G6">
         <v>4.39</v>
@@ -1773,28 +1773,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M6">
-        <v>0.06881040000000001</v>
+        <v>0.08601300000000001</v>
       </c>
       <c r="N6">
-        <v>3.997856266666667</v>
+        <v>3.980653666666667</v>
       </c>
       <c r="O6">
-        <v>0.3997856266666668</v>
+        <v>0.3980653666666668</v>
       </c>
       <c r="P6">
-        <v>3.598070640000001</v>
+        <v>3.582588300000001</v>
       </c>
       <c r="Q6">
-        <v>6.89807064</v>
+        <v>6.8825883</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08528296776482698</v>
+        <v>0.08565851913862051</v>
       </c>
       <c r="T6">
-        <v>0.6107889542334098</v>
+        <v>0.6165986145463463</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>59.09959347230458</v>
+        <v>47.27967477784367</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08363909318168948</v>
+        <v>0.08359573730914509</v>
       </c>
       <c r="C7">
-        <v>35.47182972911072</v>
+        <v>35.14338348967746</v>
       </c>
       <c r="D7">
-        <v>32.79182972911072</v>
+        <v>32.80538348967746</v>
       </c>
       <c r="E7">
-        <v>-19.39</v>
+        <v>-19.048</v>
       </c>
       <c r="F7">
-        <v>1.71</v>
+        <v>2.052</v>
       </c>
       <c r="G7">
         <v>4.39</v>
@@ -1855,28 +1855,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M7">
-        <v>0.08601300000000001</v>
+        <v>0.1032156</v>
       </c>
       <c r="N7">
-        <v>3.980653666666667</v>
+        <v>3.963451066666667</v>
       </c>
       <c r="O7">
-        <v>0.3980653666666668</v>
+        <v>0.3963451066666668</v>
       </c>
       <c r="P7">
-        <v>3.582588300000001</v>
+        <v>3.567105960000001</v>
       </c>
       <c r="Q7">
-        <v>6.8825883</v>
+        <v>6.86710596</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08565851913862051</v>
+        <v>0.08604206096717562</v>
       </c>
       <c r="T7">
-        <v>0.6165986145463463</v>
+        <v>0.6225318846531754</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>47.27967477784367</v>
+        <v>39.39972898153638</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08359573730914509</v>
+        <v>0.08355238143660065</v>
       </c>
       <c r="C8">
-        <v>35.14338348967746</v>
+        <v>34.81494845915743</v>
       </c>
       <c r="D8">
-        <v>32.80538348967746</v>
+        <v>32.81894845915743</v>
       </c>
       <c r="E8">
-        <v>-19.048</v>
+        <v>-18.706</v>
       </c>
       <c r="F8">
-        <v>2.052</v>
+        <v>2.394</v>
       </c>
       <c r="G8">
         <v>4.39</v>
@@ -1937,28 +1937,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M8">
-        <v>0.1032156</v>
+        <v>0.1204182</v>
       </c>
       <c r="N8">
-        <v>3.963451066666667</v>
+        <v>3.946248466666667</v>
       </c>
       <c r="O8">
-        <v>0.3963451066666668</v>
+        <v>0.3946248466666668</v>
       </c>
       <c r="P8">
-        <v>3.567105960000001</v>
+        <v>3.55162362</v>
       </c>
       <c r="Q8">
-        <v>6.86710596</v>
+        <v>6.85162362</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08604206096717562</v>
+        <v>0.08643385100709747</v>
       </c>
       <c r="T8">
-        <v>0.6225318846531754</v>
+        <v>0.6285927519666027</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>39.39972898153639</v>
+        <v>33.77119626988834</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08355238143660067</v>
+        <v>0.08350902556405625</v>
       </c>
       <c r="C9">
-        <v>34.81494845915743</v>
+        <v>34.48652465146098</v>
       </c>
       <c r="D9">
-        <v>32.81894845915743</v>
+        <v>32.83252465146097</v>
       </c>
       <c r="E9">
-        <v>-18.706</v>
+        <v>-18.364</v>
       </c>
       <c r="F9">
-        <v>2.394000000000001</v>
+        <v>2.736</v>
       </c>
       <c r="G9">
         <v>4.39</v>
@@ -2019,28 +2019,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M9">
-        <v>0.1204182</v>
+        <v>0.1376208</v>
       </c>
       <c r="N9">
-        <v>3.946248466666667</v>
+        <v>3.929045866666667</v>
       </c>
       <c r="O9">
-        <v>0.3946248466666668</v>
+        <v>0.3929045866666667</v>
       </c>
       <c r="P9">
-        <v>3.55162362</v>
+        <v>3.536141280000001</v>
       </c>
       <c r="Q9">
-        <v>6.85162362</v>
+        <v>6.836141280000001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0864338510070975</v>
+        <v>0.08683415822180027</v>
       </c>
       <c r="T9">
-        <v>0.6285927519666029</v>
+        <v>0.6347853772651048</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>33.77119626988833</v>
+        <v>29.54979673615229</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08350902556405625</v>
+        <v>0.08346566969151185</v>
       </c>
       <c r="C10">
-        <v>34.48652465146098</v>
+        <v>34.15811208052146</v>
       </c>
       <c r="D10">
-        <v>32.83252465146097</v>
+        <v>32.84611208052146</v>
       </c>
       <c r="E10">
-        <v>-18.364</v>
+        <v>-18.022</v>
       </c>
       <c r="F10">
-        <v>2.736</v>
+        <v>3.078</v>
       </c>
       <c r="G10">
         <v>4.39</v>
@@ -2101,28 +2101,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M10">
-        <v>0.1376208</v>
+        <v>0.1548234</v>
       </c>
       <c r="N10">
-        <v>3.929045866666667</v>
+        <v>3.911843266666667</v>
       </c>
       <c r="O10">
-        <v>0.3929045866666667</v>
+        <v>0.3911843266666667</v>
       </c>
       <c r="P10">
-        <v>3.536141280000001</v>
+        <v>3.520658940000001</v>
       </c>
       <c r="Q10">
-        <v>6.836141280000001</v>
+        <v>6.82065894</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08683415822180027</v>
+        <v>0.08724326339726576</v>
       </c>
       <c r="T10">
-        <v>0.6347853772651048</v>
+        <v>0.6411141042185188</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>29.54979673615229</v>
+        <v>26.26648598769092</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08346566969151185</v>
+        <v>0.08342231381896743</v>
       </c>
       <c r="C11">
-        <v>34.15811208052146</v>
+        <v>33.82971076029536</v>
       </c>
       <c r="D11">
-        <v>32.84611208052146</v>
+        <v>32.85971076029536</v>
       </c>
       <c r="E11">
-        <v>-18.022</v>
+        <v>-17.68</v>
       </c>
       <c r="F11">
-        <v>3.078</v>
+        <v>3.42</v>
       </c>
       <c r="G11">
         <v>4.39</v>
@@ -2183,28 +2183,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M11">
-        <v>0.1548234</v>
+        <v>0.172026</v>
       </c>
       <c r="N11">
-        <v>3.911843266666667</v>
+        <v>3.894640666666668</v>
       </c>
       <c r="O11">
-        <v>0.3911843266666667</v>
+        <v>0.3894640666666668</v>
       </c>
       <c r="P11">
-        <v>3.520658940000001</v>
+        <v>3.505176600000001</v>
       </c>
       <c r="Q11">
-        <v>6.82065894</v>
+        <v>6.805176600000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08724326339726576</v>
+        <v>0.0876614597988527</v>
       </c>
       <c r="T11">
-        <v>0.6411141042185188</v>
+        <v>0.6475834695486754</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>26.26648598769092</v>
+        <v>23.63983738892184</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08342231381896743</v>
+        <v>0.08337895794642301</v>
       </c>
       <c r="C12">
-        <v>33.82971076029536</v>
+        <v>33.50132070476224</v>
       </c>
       <c r="D12">
-        <v>32.85971076029536</v>
+        <v>32.87332070476224</v>
       </c>
       <c r="E12">
-        <v>-17.68</v>
+        <v>-17.338</v>
       </c>
       <c r="F12">
-        <v>3.42</v>
+        <v>3.762</v>
       </c>
       <c r="G12">
         <v>4.39</v>
@@ -2265,28 +2265,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M12">
-        <v>0.172026</v>
+        <v>0.1892286</v>
       </c>
       <c r="N12">
-        <v>3.894640666666668</v>
+        <v>3.877438066666667</v>
       </c>
       <c r="O12">
-        <v>0.3894640666666668</v>
+        <v>0.3877438066666667</v>
       </c>
       <c r="P12">
-        <v>3.505176600000001</v>
+        <v>3.489694260000001</v>
       </c>
       <c r="Q12">
-        <v>6.805176600000001</v>
+        <v>6.789694260000001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0876614597988527</v>
+        <v>0.0880890538723854</v>
       </c>
       <c r="T12">
-        <v>0.6475834695486754</v>
+        <v>0.6541982138750152</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>23.63983738892183</v>
+        <v>21.49076126265621</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08337895794642301</v>
+        <v>0.08333560207387861</v>
       </c>
       <c r="C13">
-        <v>33.50132070476224</v>
+        <v>33.17294192792484</v>
       </c>
       <c r="D13">
-        <v>32.87332070476224</v>
+        <v>32.88694192792484</v>
       </c>
       <c r="E13">
-        <v>-17.338</v>
+        <v>-16.996</v>
       </c>
       <c r="F13">
-        <v>3.762</v>
+        <v>4.104</v>
       </c>
       <c r="G13">
         <v>4.39</v>
@@ -2347,28 +2347,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M13">
-        <v>0.1892286</v>
+        <v>0.2064312</v>
       </c>
       <c r="N13">
-        <v>3.877438066666667</v>
+        <v>3.860235466666667</v>
       </c>
       <c r="O13">
-        <v>0.3877438066666667</v>
+        <v>0.3860235466666668</v>
       </c>
       <c r="P13">
-        <v>3.489694260000001</v>
+        <v>3.474211920000001</v>
       </c>
       <c r="Q13">
-        <v>6.789694260000001</v>
+        <v>6.774211920000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0880890538723854</v>
+        <v>0.08852636599304387</v>
       </c>
       <c r="T13">
-        <v>0.6541982138750152</v>
+        <v>0.6609632932996811</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>21.49076126265621</v>
+        <v>19.6998644907682</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08333560207387861</v>
+        <v>0.08329224620133419</v>
       </c>
       <c r="C14">
-        <v>33.17294192792484</v>
+        <v>32.84457444380913</v>
       </c>
       <c r="D14">
-        <v>32.88694192792484</v>
+        <v>32.90057444380913</v>
       </c>
       <c r="E14">
-        <v>-16.996</v>
+        <v>-16.654</v>
       </c>
       <c r="F14">
-        <v>4.104</v>
+        <v>4.446000000000001</v>
       </c>
       <c r="G14">
         <v>4.39</v>
@@ -2429,28 +2429,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M14">
-        <v>0.2064312</v>
+        <v>0.2236338</v>
       </c>
       <c r="N14">
-        <v>3.860235466666667</v>
+        <v>3.843032866666667</v>
       </c>
       <c r="O14">
-        <v>0.3860235466666668</v>
+        <v>0.3843032866666667</v>
       </c>
       <c r="P14">
-        <v>3.474211920000001</v>
+        <v>3.45872958</v>
       </c>
       <c r="Q14">
-        <v>6.774211920000001</v>
+        <v>6.758729580000001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08852636599304387</v>
+        <v>0.08897373126590136</v>
       </c>
       <c r="T14">
-        <v>0.6609632932996811</v>
+        <v>0.6678838917915805</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>19.6998644907682</v>
+        <v>18.18449029917064</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08329224620133419</v>
+        <v>0.08324889032878978</v>
       </c>
       <c r="C15">
-        <v>32.84457444380913</v>
+        <v>32.51621826646432</v>
       </c>
       <c r="D15">
-        <v>32.90057444380913</v>
+        <v>32.91421826646432</v>
       </c>
       <c r="E15">
-        <v>-16.654</v>
+        <v>-16.312</v>
       </c>
       <c r="F15">
-        <v>4.446000000000001</v>
+        <v>4.788000000000001</v>
       </c>
       <c r="G15">
         <v>4.39</v>
@@ -2511,28 +2511,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M15">
-        <v>0.2236338</v>
+        <v>0.2408364</v>
       </c>
       <c r="N15">
-        <v>3.843032866666667</v>
+        <v>3.825830266666667</v>
       </c>
       <c r="O15">
-        <v>0.3843032866666667</v>
+        <v>0.3825830266666668</v>
       </c>
       <c r="P15">
-        <v>3.45872958</v>
+        <v>3.443247240000001</v>
       </c>
       <c r="Q15">
-        <v>6.758729580000001</v>
+        <v>6.743247240000001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08897373126590136</v>
+        <v>0.08943150038231369</v>
       </c>
       <c r="T15">
-        <v>0.6678838917915805</v>
+        <v>0.6749654344344544</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>18.18449029917064</v>
+        <v>16.88559813494416</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08324889032878978</v>
+        <v>0.08320553445624537</v>
       </c>
       <c r="C16">
-        <v>32.51621826646432</v>
+        <v>32.18787340996298</v>
       </c>
       <c r="D16">
-        <v>32.91421826646432</v>
+        <v>32.92787340996298</v>
       </c>
       <c r="E16">
-        <v>-16.312</v>
+        <v>-15.97</v>
       </c>
       <c r="F16">
-        <v>4.788000000000001</v>
+        <v>5.130000000000001</v>
       </c>
       <c r="G16">
         <v>4.39</v>
@@ -2593,28 +2593,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M16">
-        <v>0.2408364</v>
+        <v>0.258039</v>
       </c>
       <c r="N16">
-        <v>3.825830266666667</v>
+        <v>3.808627666666667</v>
       </c>
       <c r="O16">
-        <v>0.3825830266666668</v>
+        <v>0.3808627666666667</v>
       </c>
       <c r="P16">
-        <v>3.443247240000001</v>
+        <v>3.427764900000001</v>
       </c>
       <c r="Q16">
-        <v>6.743247240000001</v>
+        <v>6.7277649</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08943150038231369</v>
+        <v>0.08990004053675926</v>
       </c>
       <c r="T16">
-        <v>0.6749654344344544</v>
+        <v>0.6822136016101019</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.88559813494416</v>
+        <v>15.75989159261455</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08320553445624537</v>
+        <v>0.08316217858370095</v>
       </c>
       <c r="C17">
-        <v>32.18787340996298</v>
+        <v>31.859539888401</v>
       </c>
       <c r="D17">
-        <v>32.92787340996298</v>
+        <v>32.941539888401</v>
       </c>
       <c r="E17">
-        <v>-15.97</v>
+        <v>-15.628</v>
       </c>
       <c r="F17">
-        <v>5.13</v>
+        <v>5.472</v>
       </c>
       <c r="G17">
         <v>4.39</v>
@@ -2675,28 +2675,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M17">
-        <v>0.258039</v>
+        <v>0.2752416</v>
       </c>
       <c r="N17">
-        <v>3.808627666666667</v>
+        <v>3.791425066666667</v>
       </c>
       <c r="O17">
-        <v>0.3808627666666667</v>
+        <v>0.3791425066666667</v>
       </c>
       <c r="P17">
-        <v>3.427764900000001</v>
+        <v>3.41228256</v>
       </c>
       <c r="Q17">
-        <v>6.7277649</v>
+        <v>6.71228256</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08990004053675926</v>
+        <v>0.0903797364091678</v>
       </c>
       <c r="T17">
-        <v>0.6822136016101019</v>
+        <v>0.6896343441946933</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>15.75989159261456</v>
+        <v>14.77489836807614</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08316217858370095</v>
+        <v>0.08311882271115655</v>
       </c>
       <c r="C18">
-        <v>31.859539888401</v>
+        <v>31.53121771589769</v>
       </c>
       <c r="D18">
-        <v>32.941539888401</v>
+        <v>32.95521771589769</v>
       </c>
       <c r="E18">
-        <v>-15.628</v>
+        <v>-15.286</v>
       </c>
       <c r="F18">
-        <v>5.472</v>
+        <v>5.814000000000001</v>
       </c>
       <c r="G18">
         <v>4.39</v>
@@ -2757,28 +2757,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M18">
-        <v>0.2752416</v>
+        <v>0.2924442</v>
       </c>
       <c r="N18">
-        <v>3.791425066666667</v>
+        <v>3.774222466666667</v>
       </c>
       <c r="O18">
-        <v>0.3791425066666667</v>
+        <v>0.3774222466666667</v>
       </c>
       <c r="P18">
-        <v>3.41228256</v>
+        <v>3.39680022</v>
       </c>
       <c r="Q18">
-        <v>6.71228256</v>
+        <v>6.69680022</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0903797364091678</v>
+        <v>0.09087099121826089</v>
       </c>
       <c r="T18">
-        <v>0.6896343441946933</v>
+        <v>0.6972338998536122</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.77489836807614</v>
+        <v>13.90578669936578</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08311882271115655</v>
+        <v>0.08307546683861214</v>
       </c>
       <c r="C19">
-        <v>31.53121771589769</v>
+        <v>31.20290690659583</v>
       </c>
       <c r="D19">
-        <v>32.95521771589769</v>
+        <v>32.96890690659583</v>
       </c>
       <c r="E19">
-        <v>-15.286</v>
+        <v>-14.944</v>
       </c>
       <c r="F19">
-        <v>5.814000000000001</v>
+        <v>6.156000000000001</v>
       </c>
       <c r="G19">
         <v>4.39</v>
@@ -2839,28 +2839,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M19">
-        <v>0.2924442</v>
+        <v>0.3096468000000001</v>
       </c>
       <c r="N19">
-        <v>3.774222466666667</v>
+        <v>3.757019866666667</v>
       </c>
       <c r="O19">
-        <v>0.3774222466666667</v>
+        <v>0.3757019866666668</v>
       </c>
       <c r="P19">
-        <v>3.39680022</v>
+        <v>3.381317880000001</v>
       </c>
       <c r="Q19">
-        <v>6.69680022</v>
+        <v>6.68131788</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09087099121826089</v>
+        <v>0.09137422785196601</v>
       </c>
       <c r="T19">
-        <v>0.6972338998536122</v>
+        <v>0.7050188105286023</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>13.90578669936578</v>
+        <v>13.13324299384546</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08307546683861214</v>
+        <v>0.08328861096606772</v>
       </c>
       <c r="C20">
-        <v>31.20290690659584</v>
+        <v>30.79371799520576</v>
       </c>
       <c r="D20">
-        <v>32.96890690659583</v>
+        <v>32.90171799520576</v>
       </c>
       <c r="E20">
-        <v>-14.944</v>
+        <v>-14.602</v>
       </c>
       <c r="F20">
-        <v>6.156000000000001</v>
+        <v>6.498</v>
       </c>
       <c r="G20">
         <v>4.39</v>
@@ -2921,45 +2921,45 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M20">
-        <v>0.3096468</v>
+        <v>0.3365964</v>
       </c>
       <c r="N20">
-        <v>3.757019866666667</v>
+        <v>3.730070266666667</v>
       </c>
       <c r="O20">
-        <v>0.3757019866666668</v>
+        <v>0.3730070266666667</v>
       </c>
       <c r="P20">
-        <v>3.381317880000001</v>
+        <v>3.35706324</v>
       </c>
       <c r="Q20">
-        <v>6.68131788</v>
+        <v>6.65706324</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09137422785196601</v>
+        <v>0.09188989008156509</v>
       </c>
       <c r="T20">
-        <v>0.7050188105286023</v>
+        <v>0.7129959412202587</v>
       </c>
       <c r="U20">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V20">
         <v>0.1</v>
       </c>
       <c r="W20">
-        <v>0.04527</v>
+        <v>0.04662</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y20">
-        <v>13.13324299384546</v>
+        <v>12.08172953325308</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08328861096606772</v>
+        <v>0.08325875509352332</v>
       </c>
       <c r="C21">
-        <v>30.79371799520576</v>
+        <v>30.46111289216457</v>
       </c>
       <c r="D21">
-        <v>32.90171799520576</v>
+        <v>32.91111289216457</v>
       </c>
       <c r="E21">
-        <v>-14.602</v>
+        <v>-14.26</v>
       </c>
       <c r="F21">
-        <v>6.498</v>
+        <v>6.840000000000001</v>
       </c>
       <c r="G21">
         <v>4.39</v>
@@ -3003,28 +3003,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M21">
-        <v>0.3365964</v>
+        <v>0.354312</v>
       </c>
       <c r="N21">
-        <v>3.730070266666667</v>
+        <v>3.712354666666667</v>
       </c>
       <c r="O21">
-        <v>0.3730070266666667</v>
+        <v>0.3712354666666667</v>
       </c>
       <c r="P21">
-        <v>3.35706324</v>
+        <v>3.341119200000001</v>
       </c>
       <c r="Q21">
-        <v>6.65706324</v>
+        <v>6.6411192</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09188989008156509</v>
+        <v>0.09241844386690415</v>
       </c>
       <c r="T21">
-        <v>0.7129959412202587</v>
+        <v>0.7211725001792068</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>12.08172953325308</v>
+        <v>11.47764305659043</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08325875509352332</v>
+        <v>0.0832288992209789</v>
       </c>
       <c r="C22">
-        <v>30.46111289216457</v>
+        <v>30.12851315597379</v>
       </c>
       <c r="D22">
-        <v>32.91111289216457</v>
+        <v>32.92051315597379</v>
       </c>
       <c r="E22">
-        <v>-14.26</v>
+        <v>-13.918</v>
       </c>
       <c r="F22">
-        <v>6.840000000000001</v>
+        <v>7.182000000000001</v>
       </c>
       <c r="G22">
         <v>4.39</v>
@@ -3085,28 +3085,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M22">
-        <v>0.354312</v>
+        <v>0.3720276000000001</v>
       </c>
       <c r="N22">
-        <v>3.712354666666667</v>
+        <v>3.694639066666667</v>
       </c>
       <c r="O22">
-        <v>0.3712354666666667</v>
+        <v>0.3694639066666667</v>
       </c>
       <c r="P22">
-        <v>3.341119200000001</v>
+        <v>3.325175160000001</v>
       </c>
       <c r="Q22">
-        <v>6.6411192</v>
+        <v>6.62517516</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09241844386690415</v>
+        <v>0.09296037876073278</v>
       </c>
       <c r="T22">
-        <v>0.7211725001792068</v>
+        <v>0.7295560606307862</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.47764305659043</v>
+        <v>10.93108862532421</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0832288992209789</v>
+        <v>0.08319904334843449</v>
       </c>
       <c r="C23">
-        <v>30.12851315597379</v>
+        <v>29.79591879123347</v>
       </c>
       <c r="D23">
-        <v>32.92051315597379</v>
+        <v>32.92991879123347</v>
       </c>
       <c r="E23">
-        <v>-13.918</v>
+        <v>-13.576</v>
       </c>
       <c r="F23">
-        <v>7.182</v>
+        <v>7.524000000000001</v>
       </c>
       <c r="G23">
         <v>4.39</v>
@@ -3167,28 +3167,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M23">
-        <v>0.3720276</v>
+        <v>0.3897432</v>
       </c>
       <c r="N23">
-        <v>3.694639066666667</v>
+        <v>3.676923466666667</v>
       </c>
       <c r="O23">
-        <v>0.3694639066666667</v>
+        <v>0.3676923466666668</v>
       </c>
       <c r="P23">
-        <v>3.325175160000001</v>
+        <v>3.309231120000001</v>
       </c>
       <c r="Q23">
-        <v>6.62517516</v>
+        <v>6.60923112</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09296037876073278</v>
+        <v>0.09351620942106986</v>
       </c>
       <c r="T23">
-        <v>0.7295560606307862</v>
+        <v>0.7381545841708678</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.93108862532422</v>
+        <v>10.43422096053675</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08319904334843449</v>
+        <v>0.08316918747589007</v>
       </c>
       <c r="C24">
-        <v>29.79591879123347</v>
+        <v>29.46332980254891</v>
       </c>
       <c r="D24">
-        <v>32.92991879123347</v>
+        <v>32.93932980254891</v>
       </c>
       <c r="E24">
-        <v>-13.576</v>
+        <v>-13.234</v>
       </c>
       <c r="F24">
-        <v>7.524000000000001</v>
+        <v>7.866000000000001</v>
       </c>
       <c r="G24">
         <v>4.39</v>
@@ -3249,28 +3249,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M24">
-        <v>0.3897432</v>
+        <v>0.4074588000000001</v>
       </c>
       <c r="N24">
-        <v>3.676923466666667</v>
+        <v>3.659207866666667</v>
       </c>
       <c r="O24">
-        <v>0.3676923466666668</v>
+        <v>0.3659207866666667</v>
       </c>
       <c r="P24">
-        <v>3.309231120000001</v>
+        <v>3.293287080000001</v>
       </c>
       <c r="Q24">
-        <v>6.60923112</v>
+        <v>6.593287080000001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09351620942106986</v>
+        <v>0.09408647724141568</v>
       </c>
       <c r="T24">
-        <v>0.7381545841708678</v>
+        <v>0.7469764459847177</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.43422096053675</v>
+        <v>9.980559179643848</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08316918747589007</v>
+        <v>0.08350653160334566</v>
       </c>
       <c r="C25">
-        <v>29.46332980254891</v>
+        <v>29.01530593668182</v>
       </c>
       <c r="D25">
-        <v>32.93932980254891</v>
+        <v>32.83330593668182</v>
       </c>
       <c r="E25">
-        <v>-13.234</v>
+        <v>-12.892</v>
       </c>
       <c r="F25">
-        <v>7.866000000000001</v>
+        <v>8.208000000000002</v>
       </c>
       <c r="G25">
         <v>4.39</v>
@@ -3331,45 +3331,45 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M25">
-        <v>0.4074588000000001</v>
+        <v>0.4391280000000001</v>
       </c>
       <c r="N25">
-        <v>3.659207866666667</v>
+        <v>3.627538666666667</v>
       </c>
       <c r="O25">
-        <v>0.3659207866666667</v>
+        <v>0.3627538666666668</v>
       </c>
       <c r="P25">
-        <v>3.293287080000001</v>
+        <v>3.2647848</v>
       </c>
       <c r="Q25">
-        <v>6.593287080000001</v>
+        <v>6.5647848</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09408647724141568</v>
+        <v>0.09467175210966534</v>
       </c>
       <c r="T25">
-        <v>0.7469764459847177</v>
+        <v>0.7560304620568268</v>
       </c>
       <c r="U25">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V25">
         <v>0.1</v>
       </c>
       <c r="W25">
-        <v>0.04662</v>
+        <v>0.04815</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>9.980559179643848</v>
+        <v>9.260777419491962</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08350653160334566</v>
+        <v>0.08349197573080125</v>
       </c>
       <c r="C26">
-        <v>29.01530593668182</v>
+        <v>28.67786660933201</v>
       </c>
       <c r="D26">
-        <v>32.83330593668182</v>
+        <v>32.83786660933201</v>
       </c>
       <c r="E26">
-        <v>-12.892</v>
+        <v>-12.55</v>
       </c>
       <c r="F26">
-        <v>8.208</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="G26">
         <v>4.39</v>
@@ -3413,28 +3413,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M26">
-        <v>0.439128</v>
+        <v>0.457425</v>
       </c>
       <c r="N26">
-        <v>3.627538666666667</v>
+        <v>3.609241666666667</v>
       </c>
       <c r="O26">
-        <v>0.3627538666666668</v>
+        <v>0.3609241666666667</v>
       </c>
       <c r="P26">
-        <v>3.2647848</v>
+        <v>3.248317500000001</v>
       </c>
       <c r="Q26">
-        <v>6.5647848</v>
+        <v>6.5483175</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09467175210966534</v>
+        <v>0.095272634307735</v>
       </c>
       <c r="T26">
-        <v>0.7560304620568268</v>
+        <v>0.7653259185575255</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>9.260777419491964</v>
+        <v>8.890346322712285</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08349197573080125</v>
+        <v>0.08347741985825685</v>
       </c>
       <c r="C27">
-        <v>28.67786660933201</v>
+        <v>28.34042854914821</v>
       </c>
       <c r="D27">
-        <v>32.83786660933201</v>
+        <v>32.84242854914822</v>
       </c>
       <c r="E27">
-        <v>-12.55</v>
+        <v>-12.208</v>
       </c>
       <c r="F27">
-        <v>8.550000000000001</v>
+        <v>8.892000000000001</v>
       </c>
       <c r="G27">
         <v>4.39</v>
@@ -3495,28 +3495,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M27">
-        <v>0.457425</v>
+        <v>0.475722</v>
       </c>
       <c r="N27">
-        <v>3.609241666666667</v>
+        <v>3.590944666666667</v>
       </c>
       <c r="O27">
-        <v>0.3609241666666667</v>
+        <v>0.3590944666666667</v>
       </c>
       <c r="P27">
-        <v>3.248317500000001</v>
+        <v>3.2318502</v>
       </c>
       <c r="Q27">
-        <v>6.5483175</v>
+        <v>6.5318502</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.095272634307735</v>
+        <v>0.09588975656521195</v>
       </c>
       <c r="T27">
-        <v>0.7653259185575255</v>
+        <v>0.7748726036122972</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.890346322712285</v>
+        <v>8.54840992568489</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08347741985825685</v>
+        <v>0.08346286398571244</v>
       </c>
       <c r="C28">
-        <v>28.34042854914821</v>
+        <v>28.00299175665862</v>
       </c>
       <c r="D28">
-        <v>32.84242854914822</v>
+        <v>32.84699175665862</v>
       </c>
       <c r="E28">
-        <v>-12.208</v>
+        <v>-11.866</v>
       </c>
       <c r="F28">
-        <v>8.892000000000001</v>
+        <v>9.234000000000002</v>
       </c>
       <c r="G28">
         <v>4.39</v>
@@ -3577,28 +3577,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M28">
-        <v>0.475722</v>
+        <v>0.4940190000000001</v>
       </c>
       <c r="N28">
-        <v>3.590944666666667</v>
+        <v>3.572647666666667</v>
       </c>
       <c r="O28">
-        <v>0.3590944666666667</v>
+        <v>0.3572647666666667</v>
       </c>
       <c r="P28">
-        <v>3.2318502</v>
+        <v>3.2153829</v>
       </c>
       <c r="Q28">
-        <v>6.5318502</v>
+        <v>6.515382900000001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09588975656521195</v>
+        <v>0.09652378628179786</v>
       </c>
       <c r="T28">
-        <v>0.7748726036122972</v>
+        <v>0.784680841682268</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.54840992568489</v>
+        <v>8.231802150659522</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08346286398571244</v>
+        <v>0.08344830811316803</v>
       </c>
       <c r="C29">
-        <v>28.00299175665862</v>
+        <v>27.66555623239171</v>
       </c>
       <c r="D29">
-        <v>32.84699175665862</v>
+        <v>32.85155623239171</v>
       </c>
       <c r="E29">
-        <v>-11.866</v>
+        <v>-11.524</v>
       </c>
       <c r="F29">
-        <v>9.234000000000002</v>
+        <v>9.576000000000002</v>
       </c>
       <c r="G29">
         <v>4.39</v>
@@ -3659,28 +3659,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M29">
-        <v>0.4940190000000001</v>
+        <v>0.5123160000000001</v>
       </c>
       <c r="N29">
-        <v>3.572647666666667</v>
+        <v>3.554350666666667</v>
       </c>
       <c r="O29">
-        <v>0.3572647666666667</v>
+        <v>0.3554350666666667</v>
       </c>
       <c r="P29">
-        <v>3.2153829</v>
+        <v>3.1989156</v>
       </c>
       <c r="Q29">
-        <v>6.515382900000001</v>
+        <v>6.4989156</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09652378628179786</v>
+        <v>0.09717542793495558</v>
       </c>
       <c r="T29">
-        <v>0.784680841682268</v>
+        <v>0.794761530809738</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.231802150659522</v>
+        <v>7.937809216707397</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08344830811316803</v>
+        <v>0.08343375224062362</v>
       </c>
       <c r="C30">
-        <v>27.66555623239171</v>
+        <v>27.32812197687624</v>
       </c>
       <c r="D30">
-        <v>32.85155623239171</v>
+        <v>32.85612197687625</v>
       </c>
       <c r="E30">
-        <v>-11.524</v>
+        <v>-11.182</v>
       </c>
       <c r="F30">
-        <v>9.576000000000002</v>
+        <v>9.918000000000003</v>
       </c>
       <c r="G30">
         <v>4.39</v>
@@ -3741,28 +3741,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M30">
-        <v>0.5123160000000001</v>
+        <v>0.5306130000000001</v>
       </c>
       <c r="N30">
-        <v>3.554350666666667</v>
+        <v>3.536053666666667</v>
       </c>
       <c r="O30">
-        <v>0.3554350666666667</v>
+        <v>0.3536053666666668</v>
       </c>
       <c r="P30">
-        <v>3.1989156</v>
+        <v>3.1824483</v>
       </c>
       <c r="Q30">
-        <v>6.4989156</v>
+        <v>6.4824483</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09717542793495558</v>
+        <v>0.09784542569101917</v>
       </c>
       <c r="T30">
-        <v>0.794761530809738</v>
+        <v>0.8051261830112214</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.937809216707397</v>
+        <v>7.664091657510589</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0834337522406236</v>
+        <v>0.08363519636807917</v>
       </c>
       <c r="C31">
-        <v>27.32812197687625</v>
+        <v>26.92304747920184</v>
       </c>
       <c r="D31">
-        <v>32.85612197687625</v>
+        <v>32.79304747920184</v>
       </c>
       <c r="E31">
-        <v>-11.182</v>
+        <v>-10.84</v>
       </c>
       <c r="F31">
-        <v>9.917999999999999</v>
+        <v>10.26</v>
       </c>
       <c r="G31">
         <v>4.39</v>
@@ -3823,45 +3823,45 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M31">
-        <v>0.530613</v>
+        <v>0.557118</v>
       </c>
       <c r="N31">
-        <v>3.536053666666668</v>
+        <v>3.509548666666667</v>
       </c>
       <c r="O31">
-        <v>0.3536053666666668</v>
+        <v>0.3509548666666668</v>
       </c>
       <c r="P31">
-        <v>3.182448300000001</v>
+        <v>3.158593800000001</v>
       </c>
       <c r="Q31">
-        <v>6.482448300000001</v>
+        <v>6.458593800000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09784542569101916</v>
+        <v>0.09853456624011313</v>
       </c>
       <c r="T31">
-        <v>0.8051261830112212</v>
+        <v>0.8157869681327469</v>
       </c>
       <c r="U31">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V31">
         <v>0.1</v>
       </c>
       <c r="W31">
-        <v>0.04815</v>
+        <v>0.04887</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y31">
-        <v>7.664091657510592</v>
+        <v>7.29947096785002</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08363519636807917</v>
+        <v>0.08362784049553477</v>
       </c>
       <c r="C32">
-        <v>26.92304747920184</v>
+        <v>26.58334642803538</v>
       </c>
       <c r="D32">
-        <v>32.79304747920184</v>
+        <v>32.79534642803538</v>
       </c>
       <c r="E32">
-        <v>-10.84</v>
+        <v>-10.498</v>
       </c>
       <c r="F32">
-        <v>10.26</v>
+        <v>10.602</v>
       </c>
       <c r="G32">
         <v>4.39</v>
@@ -3905,28 +3905,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M32">
-        <v>0.557118</v>
+        <v>0.5756886</v>
       </c>
       <c r="N32">
-        <v>3.509548666666667</v>
+        <v>3.490978066666667</v>
       </c>
       <c r="O32">
-        <v>0.3509548666666668</v>
+        <v>0.3490978066666668</v>
       </c>
       <c r="P32">
-        <v>3.158593800000001</v>
+        <v>3.141880260000001</v>
       </c>
       <c r="Q32">
-        <v>6.458593800000001</v>
+        <v>6.44188026</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09853456624011313</v>
+        <v>0.09924368187758664</v>
       </c>
       <c r="T32">
-        <v>0.8157869681327469</v>
+        <v>0.8267567615186647</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.29947096785002</v>
+        <v>7.064004162435503</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08362784049553477</v>
+        <v>0.08362048462299036</v>
       </c>
       <c r="C33">
-        <v>26.58334642803538</v>
+        <v>26.24364569922604</v>
       </c>
       <c r="D33">
-        <v>32.79534642803538</v>
+        <v>32.79764569922605</v>
       </c>
       <c r="E33">
-        <v>-10.498</v>
+        <v>-10.156</v>
       </c>
       <c r="F33">
-        <v>10.602</v>
+        <v>10.944</v>
       </c>
       <c r="G33">
         <v>4.39</v>
@@ -3987,28 +3987,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M33">
-        <v>0.5756886</v>
+        <v>0.5942592000000001</v>
       </c>
       <c r="N33">
-        <v>3.490978066666667</v>
+        <v>3.472407466666667</v>
       </c>
       <c r="O33">
-        <v>0.3490978066666668</v>
+        <v>0.3472407466666667</v>
       </c>
       <c r="P33">
-        <v>3.141880260000001</v>
+        <v>3.12516672</v>
       </c>
       <c r="Q33">
-        <v>6.44188026</v>
+        <v>6.42516672</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09924368187758664</v>
+        <v>0.09997365385733878</v>
       </c>
       <c r="T33">
-        <v>0.8267567615186647</v>
+        <v>0.8380491958865212</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.064004162435503</v>
+        <v>6.843254032359392</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08362048462299036</v>
+        <v>0.08361312875044595</v>
       </c>
       <c r="C34">
-        <v>26.24364569922604</v>
+        <v>25.90394529284165</v>
       </c>
       <c r="D34">
-        <v>32.79764569922605</v>
+        <v>32.79994529284165</v>
       </c>
       <c r="E34">
-        <v>-10.156</v>
+        <v>-9.814</v>
       </c>
       <c r="F34">
-        <v>10.944</v>
+        <v>11.286</v>
       </c>
       <c r="G34">
         <v>4.39</v>
@@ -4069,28 +4069,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M34">
-        <v>0.5942592000000001</v>
+        <v>0.6128298000000001</v>
       </c>
       <c r="N34">
-        <v>3.472407466666667</v>
+        <v>3.453836866666667</v>
       </c>
       <c r="O34">
-        <v>0.3472407466666667</v>
+        <v>0.3453836866666667</v>
       </c>
       <c r="P34">
-        <v>3.12516672</v>
+        <v>3.108453180000001</v>
       </c>
       <c r="Q34">
-        <v>6.42516672</v>
+        <v>6.40845318</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09997365385733878</v>
+        <v>0.1007254160454417</v>
       </c>
       <c r="T34">
-        <v>0.8380491958865212</v>
+        <v>0.8496787178474479</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.843254032359392</v>
+        <v>6.635882698045472</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08361312875044595</v>
+        <v>0.08360577287790155</v>
       </c>
       <c r="C35">
-        <v>25.90394529284165</v>
+        <v>25.56424520895001</v>
       </c>
       <c r="D35">
-        <v>32.79994529284165</v>
+        <v>32.80224520895</v>
       </c>
       <c r="E35">
-        <v>-9.814</v>
+        <v>-9.472</v>
       </c>
       <c r="F35">
-        <v>11.286</v>
+        <v>11.628</v>
       </c>
       <c r="G35">
         <v>4.39</v>
@@ -4151,28 +4151,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M35">
-        <v>0.6128298000000001</v>
+        <v>0.6314004000000001</v>
       </c>
       <c r="N35">
-        <v>3.453836866666667</v>
+        <v>3.435266266666667</v>
       </c>
       <c r="O35">
-        <v>0.3453836866666667</v>
+        <v>0.3435266266666668</v>
       </c>
       <c r="P35">
-        <v>3.108453180000001</v>
+        <v>3.091739640000001</v>
       </c>
       <c r="Q35">
-        <v>6.40845318</v>
+        <v>6.391739640000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1007254160454417</v>
+        <v>0.1014999589059114</v>
       </c>
       <c r="T35">
-        <v>0.8496787178474479</v>
+        <v>0.8616606495647665</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.635882698045472</v>
+        <v>6.440709677514723</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08360577287790155</v>
+        <v>0.08359841700535714</v>
       </c>
       <c r="C36">
-        <v>25.56424520895001</v>
+        <v>25.22454544761896</v>
       </c>
       <c r="D36">
-        <v>32.80224520895</v>
+        <v>32.80454544761896</v>
       </c>
       <c r="E36">
-        <v>-9.472</v>
+        <v>-9.129999999999999</v>
       </c>
       <c r="F36">
-        <v>11.628</v>
+        <v>11.97</v>
       </c>
       <c r="G36">
         <v>4.39</v>
@@ -4233,28 +4233,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M36">
-        <v>0.6314004000000001</v>
+        <v>0.6499710000000002</v>
       </c>
       <c r="N36">
-        <v>3.435266266666667</v>
+        <v>3.416695666666667</v>
       </c>
       <c r="O36">
-        <v>0.3435266266666668</v>
+        <v>0.3416695666666667</v>
       </c>
       <c r="P36">
-        <v>3.091739640000001</v>
+        <v>3.075026100000001</v>
       </c>
       <c r="Q36">
-        <v>6.391739640000001</v>
+        <v>6.3750261</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1014999589059114</v>
+        <v>0.1022983338543956</v>
       </c>
       <c r="T36">
-        <v>0.8616606495647665</v>
+        <v>0.8740112561041563</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.440709677514723</v>
+        <v>6.256689401014301</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08359841700535714</v>
+        <v>0.08391506113281272</v>
       </c>
       <c r="C37">
-        <v>25.22454544761896</v>
+        <v>24.78381943287607</v>
       </c>
       <c r="D37">
-        <v>32.80454544761896</v>
+        <v>32.70581943287607</v>
       </c>
       <c r="E37">
-        <v>-9.129999999999999</v>
+        <v>-8.787999999999998</v>
       </c>
       <c r="F37">
-        <v>11.97</v>
+        <v>12.312</v>
       </c>
       <c r="G37">
         <v>4.39</v>
@@ -4315,45 +4315,45 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M37">
-        <v>0.6499710000000002</v>
+        <v>0.6808536000000002</v>
       </c>
       <c r="N37">
-        <v>3.416695666666667</v>
+        <v>3.385813066666667</v>
       </c>
       <c r="O37">
-        <v>0.3416695666666667</v>
+        <v>0.3385813066666667</v>
       </c>
       <c r="P37">
-        <v>3.075026100000001</v>
+        <v>3.04723176</v>
       </c>
       <c r="Q37">
-        <v>6.3750261</v>
+        <v>6.34723176</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1022983338543956</v>
+        <v>0.1031216580200199</v>
       </c>
       <c r="T37">
-        <v>0.8740112561041563</v>
+        <v>0.8867478190979021</v>
       </c>
       <c r="U37">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V37">
         <v>0.1</v>
       </c>
       <c r="W37">
-        <v>0.04887</v>
+        <v>0.04977</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y37">
-        <v>6.256689401014301</v>
+        <v>5.972894417634961</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08391506113281272</v>
+        <v>0.0839167052602683</v>
       </c>
       <c r="C38">
-        <v>24.78381943287607</v>
+        <v>24.44130836348149</v>
       </c>
       <c r="D38">
-        <v>32.70581943287607</v>
+        <v>32.70530836348149</v>
       </c>
       <c r="E38">
-        <v>-8.788</v>
+        <v>-8.446</v>
       </c>
       <c r="F38">
-        <v>12.312</v>
+        <v>12.654</v>
       </c>
       <c r="G38">
         <v>4.39</v>
@@ -4397,28 +4397,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M38">
-        <v>0.6808536000000001</v>
+        <v>0.6997662000000001</v>
       </c>
       <c r="N38">
-        <v>3.385813066666667</v>
+        <v>3.366900466666667</v>
       </c>
       <c r="O38">
-        <v>0.3385813066666667</v>
+        <v>0.3366900466666667</v>
       </c>
       <c r="P38">
-        <v>3.047231760000001</v>
+        <v>3.03021042</v>
       </c>
       <c r="Q38">
-        <v>6.347231760000001</v>
+        <v>6.33021042</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1031216580200199</v>
+        <v>0.1039711194607433</v>
       </c>
       <c r="T38">
-        <v>0.8867478190979021</v>
+        <v>0.8998887174247826</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.972894417634961</v>
+        <v>5.811464838779962</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.0839167052602683</v>
+        <v>0.0839183493877239</v>
       </c>
       <c r="C39">
-        <v>24.44130836348149</v>
+        <v>24.09879731005886</v>
       </c>
       <c r="D39">
-        <v>32.70530836348149</v>
+        <v>32.70479731005886</v>
       </c>
       <c r="E39">
-        <v>-8.446</v>
+        <v>-8.104000000000001</v>
       </c>
       <c r="F39">
-        <v>12.654</v>
+        <v>12.996</v>
       </c>
       <c r="G39">
         <v>4.39</v>
@@ -4479,28 +4479,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M39">
-        <v>0.6997662000000001</v>
+        <v>0.7186788000000001</v>
       </c>
       <c r="N39">
-        <v>3.366900466666667</v>
+        <v>3.347987866666667</v>
       </c>
       <c r="O39">
-        <v>0.3366900466666667</v>
+        <v>0.3347987866666667</v>
       </c>
       <c r="P39">
-        <v>3.03021042</v>
+        <v>3.013189080000001</v>
       </c>
       <c r="Q39">
-        <v>6.33021042</v>
+        <v>6.313189080000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1039711194607433</v>
+        <v>0.1048479828834256</v>
       </c>
       <c r="T39">
-        <v>0.8998887174247826</v>
+        <v>0.9134535156976917</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.811464838779962</v>
+        <v>5.658531553548911</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0839183493877239</v>
+        <v>0.08391999351517949</v>
       </c>
       <c r="C40">
-        <v>24.09879731005886</v>
+        <v>23.75628627260744</v>
       </c>
       <c r="D40">
-        <v>32.70479731005886</v>
+        <v>32.70428627260744</v>
       </c>
       <c r="E40">
-        <v>-8.104000000000001</v>
+        <v>-7.762</v>
       </c>
       <c r="F40">
-        <v>12.996</v>
+        <v>13.338</v>
       </c>
       <c r="G40">
         <v>4.39</v>
@@ -4561,28 +4561,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M40">
-        <v>0.7186788000000001</v>
+        <v>0.7375914000000001</v>
       </c>
       <c r="N40">
-        <v>3.347987866666667</v>
+        <v>3.329075266666667</v>
       </c>
       <c r="O40">
-        <v>0.3347987866666667</v>
+        <v>0.3329075266666667</v>
       </c>
       <c r="P40">
-        <v>3.013189080000001</v>
+        <v>2.99616774</v>
       </c>
       <c r="Q40">
-        <v>6.313189080000001</v>
+        <v>6.29616774</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1048479828834256</v>
+        <v>0.1057535959265238</v>
       </c>
       <c r="T40">
-        <v>0.9134535156976917</v>
+        <v>0.9274630614549583</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.658531553548911</v>
+        <v>5.51344100089381</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08391999351517949</v>
+        <v>0.08392163764263508</v>
       </c>
       <c r="C41">
-        <v>23.75628627260744</v>
+        <v>23.41377525112647</v>
       </c>
       <c r="D41">
-        <v>32.70428627260744</v>
+        <v>32.70377525112647</v>
       </c>
       <c r="E41">
-        <v>-7.762</v>
+        <v>-7.42</v>
       </c>
       <c r="F41">
-        <v>13.338</v>
+        <v>13.68</v>
       </c>
       <c r="G41">
         <v>4.39</v>
@@ -4643,28 +4643,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M41">
-        <v>0.7375914000000001</v>
+        <v>0.7565040000000001</v>
       </c>
       <c r="N41">
-        <v>3.329075266666667</v>
+        <v>3.310162666666667</v>
       </c>
       <c r="O41">
-        <v>0.3329075266666667</v>
+        <v>0.3310162666666667</v>
       </c>
       <c r="P41">
-        <v>2.99616774</v>
+        <v>2.9791464</v>
       </c>
       <c r="Q41">
-        <v>6.29616774</v>
+        <v>6.2791464</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1057535959265238</v>
+        <v>0.1066893960710585</v>
       </c>
       <c r="T41">
-        <v>0.9274630614549583</v>
+        <v>0.9419395920708006</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.51344100089381</v>
+        <v>5.375604975871465</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08392163764263508</v>
+        <v>0.08392328177009067</v>
       </c>
       <c r="C42">
-        <v>23.41377525112647</v>
+        <v>23.07126424561519</v>
       </c>
       <c r="D42">
-        <v>32.70377525112647</v>
+        <v>32.70326424561519</v>
       </c>
       <c r="E42">
-        <v>-7.42</v>
+        <v>-7.077999999999999</v>
       </c>
       <c r="F42">
-        <v>13.68</v>
+        <v>14.022</v>
       </c>
       <c r="G42">
         <v>4.39</v>
@@ -4725,28 +4725,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M42">
-        <v>0.7565040000000001</v>
+        <v>0.7754166000000001</v>
       </c>
       <c r="N42">
-        <v>3.310162666666667</v>
+        <v>3.291250066666667</v>
       </c>
       <c r="O42">
-        <v>0.3310162666666667</v>
+        <v>0.3291250066666667</v>
       </c>
       <c r="P42">
-        <v>2.9791464</v>
+        <v>2.96212506</v>
       </c>
       <c r="Q42">
-        <v>6.2791464</v>
+        <v>6.262125060000001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1066893960710585</v>
+        <v>0.107656918254391</v>
       </c>
       <c r="T42">
-        <v>0.9419395920708006</v>
+        <v>0.9569068525380273</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.375604975871465</v>
+        <v>5.244492659386795</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08392328177009067</v>
+        <v>0.08392492589754626</v>
       </c>
       <c r="C43">
-        <v>23.07126424561519</v>
+        <v>22.72875325607288</v>
       </c>
       <c r="D43">
-        <v>32.70326424561519</v>
+        <v>32.70275325607288</v>
       </c>
       <c r="E43">
-        <v>-7.077999999999999</v>
+        <v>-6.735999999999999</v>
       </c>
       <c r="F43">
-        <v>14.022</v>
+        <v>14.364</v>
       </c>
       <c r="G43">
         <v>4.39</v>
@@ -4807,28 +4807,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M43">
-        <v>0.7754166000000001</v>
+        <v>0.7943292000000002</v>
       </c>
       <c r="N43">
-        <v>3.291250066666667</v>
+        <v>3.272337466666667</v>
       </c>
       <c r="O43">
-        <v>0.3291250066666667</v>
+        <v>0.3272337466666668</v>
       </c>
       <c r="P43">
-        <v>2.96212506</v>
+        <v>2.945103720000001</v>
       </c>
       <c r="Q43">
-        <v>6.262125060000001</v>
+        <v>6.24510372</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.107656918254391</v>
+        <v>0.1086578032716315</v>
       </c>
       <c r="T43">
-        <v>0.9569068525380273</v>
+        <v>0.9723902254351584</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.244492659386795</v>
+        <v>5.119623786544252</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08392492589754626</v>
+        <v>0.08392657002500184</v>
       </c>
       <c r="C44">
-        <v>22.72875325607288</v>
+        <v>22.38624228249877</v>
       </c>
       <c r="D44">
-        <v>32.70275325607288</v>
+        <v>32.70224228249877</v>
       </c>
       <c r="E44">
-        <v>-6.736000000000001</v>
+        <v>-6.394</v>
       </c>
       <c r="F44">
-        <v>14.364</v>
+        <v>14.706</v>
       </c>
       <c r="G44">
         <v>4.39</v>
@@ -4889,28 +4889,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M44">
-        <v>0.7943292000000001</v>
+        <v>0.8132418000000001</v>
       </c>
       <c r="N44">
-        <v>3.272337466666667</v>
+        <v>3.253424866666667</v>
       </c>
       <c r="O44">
-        <v>0.3272337466666668</v>
+        <v>0.3253424866666668</v>
       </c>
       <c r="P44">
-        <v>2.945103720000001</v>
+        <v>2.92808238</v>
       </c>
       <c r="Q44">
-        <v>6.24510372</v>
+        <v>6.22808238</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1086578032716315</v>
+        <v>0.1096938070614067</v>
       </c>
       <c r="T44">
-        <v>0.9723902254351583</v>
+        <v>0.9884168745742939</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.119623786544253</v>
+        <v>5.000562768252525</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08392657002500184</v>
+        <v>0.08392821415245744</v>
       </c>
       <c r="C45">
-        <v>22.38624228249877</v>
+        <v>22.04373132489213</v>
       </c>
       <c r="D45">
-        <v>32.70224228249877</v>
+        <v>32.70173132489213</v>
       </c>
       <c r="E45">
-        <v>-6.394</v>
+        <v>-6.052</v>
       </c>
       <c r="F45">
-        <v>14.706</v>
+        <v>15.048</v>
       </c>
       <c r="G45">
         <v>4.39</v>
@@ -4971,28 +4971,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M45">
-        <v>0.8132418000000001</v>
+        <v>0.8321544000000002</v>
       </c>
       <c r="N45">
-        <v>3.253424866666667</v>
+        <v>3.234512266666667</v>
       </c>
       <c r="O45">
-        <v>0.3253424866666668</v>
+        <v>0.3234512266666667</v>
       </c>
       <c r="P45">
-        <v>2.92808238</v>
+        <v>2.91106104</v>
       </c>
       <c r="Q45">
-        <v>6.22808238</v>
+        <v>6.211061040000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1096938070614067</v>
+        <v>0.1107668109865311</v>
       </c>
       <c r="T45">
-        <v>0.9884168745742939</v>
+        <v>1.005015904039827</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.000562768252525</v>
+        <v>4.886913614428604</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08392821415245744</v>
+        <v>0.08392985827991302</v>
       </c>
       <c r="C46">
-        <v>22.04373132489213</v>
+        <v>21.70122038325218</v>
       </c>
       <c r="D46">
-        <v>32.70173132489213</v>
+        <v>32.70122038325218</v>
       </c>
       <c r="E46">
-        <v>-6.052</v>
+        <v>-5.709999999999999</v>
       </c>
       <c r="F46">
-        <v>15.048</v>
+        <v>15.39</v>
       </c>
       <c r="G46">
         <v>4.39</v>
@@ -5053,28 +5053,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M46">
-        <v>0.8321544000000002</v>
+        <v>0.8510670000000001</v>
       </c>
       <c r="N46">
-        <v>3.234512266666667</v>
+        <v>3.215599666666667</v>
       </c>
       <c r="O46">
-        <v>0.3234512266666667</v>
+        <v>0.3215599666666668</v>
       </c>
       <c r="P46">
-        <v>2.91106104</v>
+        <v>2.8940397</v>
       </c>
       <c r="Q46">
-        <v>6.211061040000001</v>
+        <v>6.1940397</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1107668109865311</v>
+        <v>0.1118788332362055</v>
       </c>
       <c r="T46">
-        <v>1.005015904039827</v>
+        <v>1.022218534576835</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.886913614428604</v>
+        <v>4.778315534107969</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08392985827991302</v>
+        <v>0.08393150240736862</v>
       </c>
       <c r="C47">
-        <v>21.70122038325218</v>
+        <v>21.3587094575782</v>
       </c>
       <c r="D47">
-        <v>32.70122038325218</v>
+        <v>32.70070945757821</v>
       </c>
       <c r="E47">
-        <v>-5.709999999999999</v>
+        <v>-5.367999999999999</v>
       </c>
       <c r="F47">
-        <v>15.39</v>
+        <v>15.732</v>
       </c>
       <c r="G47">
         <v>4.39</v>
@@ -5135,28 +5135,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M47">
-        <v>0.8510670000000001</v>
+        <v>0.8699796000000002</v>
       </c>
       <c r="N47">
-        <v>3.215599666666667</v>
+        <v>3.196687066666667</v>
       </c>
       <c r="O47">
-        <v>0.3215599666666668</v>
+        <v>0.3196687066666667</v>
       </c>
       <c r="P47">
-        <v>2.8940397</v>
+        <v>2.877018360000001</v>
       </c>
       <c r="Q47">
-        <v>6.1940397</v>
+        <v>6.17701836</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1118788332362055</v>
+        <v>0.1130320414951271</v>
       </c>
       <c r="T47">
-        <v>1.022218534576835</v>
+        <v>1.040058299578176</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.778315534107969</v>
+        <v>4.674439109453448</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08393150240736862</v>
+        <v>0.0839331465348242</v>
       </c>
       <c r="C48">
-        <v>21.3587094575782</v>
+        <v>21.01619854786944</v>
       </c>
       <c r="D48">
-        <v>32.70070945757821</v>
+        <v>32.70019854786944</v>
       </c>
       <c r="E48">
-        <v>-5.367999999999999</v>
+        <v>-5.026</v>
       </c>
       <c r="F48">
-        <v>15.732</v>
+        <v>16.074</v>
       </c>
       <c r="G48">
         <v>4.39</v>
@@ -5217,28 +5217,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M48">
-        <v>0.8699796000000002</v>
+        <v>0.8888922000000001</v>
       </c>
       <c r="N48">
-        <v>3.196687066666667</v>
+        <v>3.177774466666667</v>
       </c>
       <c r="O48">
-        <v>0.3196687066666667</v>
+        <v>0.3177774466666667</v>
       </c>
       <c r="P48">
-        <v>2.877018360000001</v>
+        <v>2.859997020000001</v>
       </c>
       <c r="Q48">
-        <v>6.17701836</v>
+        <v>6.15999702</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1130320414951271</v>
+        <v>0.1142287670468381</v>
       </c>
       <c r="T48">
-        <v>1.040058299578176</v>
+        <v>1.058571263258812</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.674439109453448</v>
+        <v>4.574982958188481</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.0839331465348242</v>
+        <v>0.08501479066227981</v>
       </c>
       <c r="C49">
-        <v>21.01619854786944</v>
+        <v>20.3415044381792</v>
       </c>
       <c r="D49">
-        <v>32.70019854786944</v>
+        <v>32.3675044381792</v>
       </c>
       <c r="E49">
-        <v>-5.026</v>
+        <v>-4.683999999999997</v>
       </c>
       <c r="F49">
-        <v>16.074</v>
+        <v>16.416</v>
       </c>
       <c r="G49">
         <v>4.39</v>
@@ -5299,45 +5299,45 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M49">
-        <v>0.8888922000000001</v>
+        <v>0.9488448000000003</v>
       </c>
       <c r="N49">
-        <v>3.177774466666667</v>
+        <v>3.117821866666667</v>
       </c>
       <c r="O49">
-        <v>0.3177774466666667</v>
+        <v>0.3117821866666667</v>
       </c>
       <c r="P49">
-        <v>2.859997020000001</v>
+        <v>2.80603968</v>
       </c>
       <c r="Q49">
-        <v>6.15999702</v>
+        <v>6.10603968</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1142287670468381</v>
+        <v>0.1154715205043842</v>
       </c>
       <c r="T49">
-        <v>1.058571263258812</v>
+        <v>1.077796264004089</v>
       </c>
       <c r="U49">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V49">
         <v>0.1</v>
       </c>
       <c r="W49">
-        <v>0.04977</v>
+        <v>0.05202</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y49">
-        <v>4.574982958188481</v>
+        <v>4.285913425110899</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08501479066227979</v>
+        <v>0.08503893478973538</v>
       </c>
       <c r="C50">
-        <v>20.34150443817921</v>
+        <v>19.99215536725604</v>
       </c>
       <c r="D50">
-        <v>32.36750443817921</v>
+        <v>32.36015536725604</v>
       </c>
       <c r="E50">
-        <v>-4.684000000000001</v>
+        <v>-4.341999999999999</v>
       </c>
       <c r="F50">
-        <v>16.416</v>
+        <v>16.758</v>
       </c>
       <c r="G50">
         <v>4.39</v>
@@ -5381,28 +5381,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M50">
-        <v>0.9488448</v>
+        <v>0.9686124000000003</v>
       </c>
       <c r="N50">
-        <v>3.117821866666667</v>
+        <v>3.098054266666667</v>
       </c>
       <c r="O50">
-        <v>0.3117821866666668</v>
+        <v>0.3098054266666667</v>
       </c>
       <c r="P50">
-        <v>2.80603968</v>
+        <v>2.78824884</v>
       </c>
       <c r="Q50">
-        <v>6.10603968</v>
+        <v>6.08824884</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1154715205043842</v>
+        <v>0.116763009391638</v>
       </c>
       <c r="T50">
-        <v>1.077796264004089</v>
+        <v>1.09777518634722</v>
       </c>
       <c r="U50">
         <v>0.0578</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.2859134251109</v>
+        <v>4.198445804190269</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08503893478973538</v>
+        <v>0.08506307891719096</v>
       </c>
       <c r="C51">
-        <v>19.99215536725604</v>
+        <v>19.64280963280162</v>
       </c>
       <c r="D51">
-        <v>32.36015536725604</v>
+        <v>32.35280963280162</v>
       </c>
       <c r="E51">
-        <v>-4.341999999999999</v>
+        <v>-4</v>
       </c>
       <c r="F51">
-        <v>16.758</v>
+        <v>17.1</v>
       </c>
       <c r="G51">
         <v>4.39</v>
@@ -5463,28 +5463,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M51">
-        <v>0.9686124000000003</v>
+        <v>0.9883800000000001</v>
       </c>
       <c r="N51">
-        <v>3.098054266666667</v>
+        <v>3.078286666666667</v>
       </c>
       <c r="O51">
-        <v>0.3098054266666667</v>
+        <v>0.3078286666666668</v>
       </c>
       <c r="P51">
-        <v>2.78824884</v>
+        <v>2.770458000000001</v>
       </c>
       <c r="Q51">
-        <v>6.08824884</v>
+        <v>6.070458</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.116763009391638</v>
+        <v>0.1181061578343819</v>
       </c>
       <c r="T51">
-        <v>1.09777518634722</v>
+        <v>1.118553265584076</v>
       </c>
       <c r="U51">
         <v>0.0578</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.198445804190269</v>
+        <v>4.114476888106464</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08506307891719096</v>
+        <v>0.08508722304464655</v>
       </c>
       <c r="C52">
-        <v>19.64280963280162</v>
+        <v>19.29346723254432</v>
       </c>
       <c r="D52">
-        <v>32.35280963280162</v>
+        <v>32.34546723254432</v>
       </c>
       <c r="E52">
-        <v>-4</v>
+        <v>-3.658000000000001</v>
       </c>
       <c r="F52">
-        <v>17.1</v>
+        <v>17.442</v>
       </c>
       <c r="G52">
         <v>4.39</v>
@@ -5545,28 +5545,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M52">
-        <v>0.9883800000000001</v>
+        <v>1.0081476</v>
       </c>
       <c r="N52">
-        <v>3.078286666666667</v>
+        <v>3.058519066666667</v>
       </c>
       <c r="O52">
-        <v>0.3078286666666668</v>
+        <v>0.3058519066666667</v>
       </c>
       <c r="P52">
-        <v>2.770458000000001</v>
+        <v>2.752667160000001</v>
       </c>
       <c r="Q52">
-        <v>6.070458</v>
+        <v>6.05266716</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1181061578343819</v>
+        <v>0.119504128662544</v>
       </c>
       <c r="T52">
-        <v>1.118553265584076</v>
+        <v>1.140179429687742</v>
       </c>
       <c r="U52">
         <v>0.0578</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.114476888106464</v>
+        <v>4.033800870692613</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08508722304464655</v>
+        <v>0.08674936717210213</v>
       </c>
       <c r="C53">
-        <v>19.29346723254432</v>
+        <v>18.45388618479427</v>
       </c>
       <c r="D53">
-        <v>32.34546723254432</v>
+        <v>31.84788618479428</v>
       </c>
       <c r="E53">
-        <v>-3.658000000000001</v>
+        <v>-3.315999999999999</v>
       </c>
       <c r="F53">
-        <v>17.442</v>
+        <v>17.784</v>
       </c>
       <c r="G53">
         <v>4.39</v>
@@ -5627,45 +5627,45 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M53">
-        <v>1.0081476</v>
+        <v>1.0901592</v>
       </c>
       <c r="N53">
-        <v>3.058519066666667</v>
+        <v>2.976507466666667</v>
       </c>
       <c r="O53">
-        <v>0.3058519066666667</v>
+        <v>0.2976507466666667</v>
       </c>
       <c r="P53">
-        <v>2.752667160000001</v>
+        <v>2.67885672</v>
       </c>
       <c r="Q53">
-        <v>6.05266716</v>
+        <v>5.97885672</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.119504128662544</v>
+        <v>0.1209603482752128</v>
       </c>
       <c r="T53">
-        <v>1.140179429687742</v>
+        <v>1.162706683962395</v>
       </c>
       <c r="U53">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V53">
         <v>0.1</v>
       </c>
       <c r="W53">
-        <v>0.05202</v>
+        <v>0.05517</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y53">
-        <v>4.033800870692613</v>
+        <v>3.730342014878805</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08674936717210213</v>
+        <v>0.08680501129955773</v>
       </c>
       <c r="C54">
-        <v>18.45388618479427</v>
+        <v>18.09549319871286</v>
       </c>
       <c r="D54">
-        <v>31.84788618479428</v>
+        <v>31.83149319871286</v>
       </c>
       <c r="E54">
-        <v>-3.315999999999999</v>
+        <v>-2.974</v>
       </c>
       <c r="F54">
-        <v>17.784</v>
+        <v>18.126</v>
       </c>
       <c r="G54">
         <v>4.39</v>
@@ -5709,28 +5709,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M54">
-        <v>1.0901592</v>
+        <v>1.1111238</v>
       </c>
       <c r="N54">
-        <v>2.976507466666667</v>
+        <v>2.955542866666667</v>
       </c>
       <c r="O54">
-        <v>0.2976507466666667</v>
+        <v>0.2955542866666667</v>
       </c>
       <c r="P54">
-        <v>2.67885672</v>
+        <v>2.65998858</v>
       </c>
       <c r="Q54">
-        <v>5.97885672</v>
+        <v>5.95998858</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1209603482752128</v>
+        <v>0.1224785346799101</v>
       </c>
       <c r="T54">
-        <v>1.162706683962395</v>
+        <v>1.186192544801926</v>
       </c>
       <c r="U54">
         <v>0.0613</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.730342014878805</v>
+        <v>3.659958203277319</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08680501129955773</v>
+        <v>0.08686065542701332</v>
       </c>
       <c r="C55">
-        <v>18.09549319871286</v>
+        <v>17.73711707979427</v>
       </c>
       <c r="D55">
-        <v>31.83149319871286</v>
+        <v>31.81511707979427</v>
       </c>
       <c r="E55">
-        <v>-2.974</v>
+        <v>-2.631999999999998</v>
       </c>
       <c r="F55">
-        <v>18.126</v>
+        <v>18.468</v>
       </c>
       <c r="G55">
         <v>4.39</v>
@@ -5791,28 +5791,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M55">
-        <v>1.1111238</v>
+        <v>1.1320884</v>
       </c>
       <c r="N55">
-        <v>2.955542866666667</v>
+        <v>2.934578266666667</v>
       </c>
       <c r="O55">
-        <v>0.2955542866666667</v>
+        <v>0.2934578266666667</v>
       </c>
       <c r="P55">
-        <v>2.65998858</v>
+        <v>2.64112044</v>
       </c>
       <c r="Q55">
-        <v>5.95998858</v>
+        <v>5.941120440000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1224785346799101</v>
+        <v>0.1240627291891594</v>
       </c>
       <c r="T55">
-        <v>1.186192544801926</v>
+        <v>1.210699530025785</v>
       </c>
       <c r="U55">
         <v>0.0613</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.659958203277319</v>
+        <v>3.592181199512924</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08686065542701332</v>
+        <v>0.08691629955446892</v>
       </c>
       <c r="C56">
-        <v>17.73711707979427</v>
+        <v>17.37875780201931</v>
       </c>
       <c r="D56">
-        <v>31.81511707979427</v>
+        <v>31.79875780201931</v>
       </c>
       <c r="E56">
-        <v>-2.631999999999998</v>
+        <v>-2.289999999999999</v>
       </c>
       <c r="F56">
-        <v>18.468</v>
+        <v>18.81</v>
       </c>
       <c r="G56">
         <v>4.39</v>
@@ -5873,28 +5873,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M56">
-        <v>1.1320884</v>
+        <v>1.153053</v>
       </c>
       <c r="N56">
-        <v>2.934578266666667</v>
+        <v>2.913613666666667</v>
       </c>
       <c r="O56">
-        <v>0.2934578266666667</v>
+        <v>0.2913613666666667</v>
       </c>
       <c r="P56">
-        <v>2.64112044</v>
+        <v>2.622252300000001</v>
       </c>
       <c r="Q56">
-        <v>5.941120440000001</v>
+        <v>5.9222523</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1240627291891594</v>
+        <v>0.1257173323432643</v>
       </c>
       <c r="T56">
-        <v>1.210699530025785</v>
+        <v>1.236295714592926</v>
       </c>
       <c r="U56">
         <v>0.0613</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.592181199512924</v>
+        <v>3.526868814067235</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08691629955446892</v>
+        <v>0.0883831436819245</v>
       </c>
       <c r="C57">
-        <v>17.37875780201931</v>
+        <v>16.61149428901102</v>
       </c>
       <c r="D57">
-        <v>31.79875780201931</v>
+        <v>31.37349428901102</v>
       </c>
       <c r="E57">
-        <v>-2.289999999999999</v>
+        <v>-1.947999999999997</v>
       </c>
       <c r="F57">
-        <v>18.81</v>
+        <v>19.152</v>
       </c>
       <c r="G57">
         <v>4.39</v>
@@ -5955,45 +5955,45 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M57">
-        <v>1.153053</v>
+        <v>1.2276432</v>
       </c>
       <c r="N57">
-        <v>2.913613666666667</v>
+        <v>2.839023466666667</v>
       </c>
       <c r="O57">
-        <v>0.2913613666666667</v>
+        <v>0.2839023466666667</v>
       </c>
       <c r="P57">
-        <v>2.622252300000001</v>
+        <v>2.55512112</v>
       </c>
       <c r="Q57">
-        <v>5.9222523</v>
+        <v>5.85512112</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1257173323432643</v>
+        <v>0.1274471447316466</v>
       </c>
       <c r="T57">
-        <v>1.236295714592926</v>
+        <v>1.263055362094937</v>
       </c>
       <c r="U57">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V57">
         <v>0.1</v>
       </c>
       <c r="W57">
-        <v>0.05517</v>
+        <v>0.05769000000000001</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y57">
-        <v>3.526868814067235</v>
+        <v>3.31258028934357</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.0883831436819245</v>
+        <v>0.08846398780938008</v>
       </c>
       <c r="C58">
-        <v>16.61149428901102</v>
+        <v>16.24638666029904</v>
       </c>
       <c r="D58">
-        <v>31.37349428901102</v>
+        <v>31.35038666029904</v>
       </c>
       <c r="E58">
-        <v>-1.947999999999997</v>
+        <v>-1.605999999999998</v>
       </c>
       <c r="F58">
-        <v>19.152</v>
+        <v>19.494</v>
       </c>
       <c r="G58">
         <v>4.39</v>
@@ -6037,28 +6037,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M58">
-        <v>1.2276432</v>
+        <v>1.2495654</v>
       </c>
       <c r="N58">
-        <v>2.839023466666667</v>
+        <v>2.817101266666667</v>
       </c>
       <c r="O58">
-        <v>0.2839023466666667</v>
+        <v>0.2817101266666667</v>
       </c>
       <c r="P58">
-        <v>2.55512112</v>
+        <v>2.53539114</v>
       </c>
       <c r="Q58">
-        <v>5.85512112</v>
+        <v>5.83539114</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1274471447316466</v>
+        <v>0.1292574135101862</v>
       </c>
       <c r="T58">
-        <v>1.263055362094937</v>
+        <v>1.291059644364484</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.31258028934357</v>
+        <v>3.254464845670876</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08846398780938008</v>
+        <v>0.08854483193683568</v>
       </c>
       <c r="C59">
-        <v>16.24638666029904</v>
+        <v>15.88131304561865</v>
       </c>
       <c r="D59">
-        <v>31.35038666029904</v>
+        <v>31.32731304561866</v>
       </c>
       <c r="E59">
-        <v>-1.605999999999998</v>
+        <v>-1.263999999999996</v>
       </c>
       <c r="F59">
-        <v>19.494</v>
+        <v>19.83600000000001</v>
       </c>
       <c r="G59">
         <v>4.39</v>
@@ -6119,28 +6119,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M59">
-        <v>1.2495654</v>
+        <v>1.2714876</v>
       </c>
       <c r="N59">
-        <v>2.817101266666667</v>
+        <v>2.795179066666667</v>
       </c>
       <c r="O59">
-        <v>0.2817101266666667</v>
+        <v>0.2795179066666667</v>
       </c>
       <c r="P59">
-        <v>2.53539114</v>
+        <v>2.51566116</v>
       </c>
       <c r="Q59">
-        <v>5.83539114</v>
+        <v>5.815661159999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1292574135101862</v>
+        <v>0.1311538855638945</v>
       </c>
       <c r="T59">
-        <v>1.291059644364484</v>
+        <v>1.320397463884962</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.254464845670876</v>
+        <v>3.198353382814481</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08854483193683568</v>
+        <v>0.08862567606429125</v>
       </c>
       <c r="C60">
-        <v>15.88131304561865</v>
+        <v>15.51627336992299</v>
       </c>
       <c r="D60">
-        <v>31.32731304561866</v>
+        <v>31.30427336992299</v>
       </c>
       <c r="E60">
-        <v>-1.264000000000003</v>
+        <v>-0.9220000000000006</v>
       </c>
       <c r="F60">
-        <v>19.836</v>
+        <v>20.178</v>
       </c>
       <c r="G60">
         <v>4.39</v>
@@ -6201,28 +6201,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M60">
-        <v>1.2714876</v>
+        <v>1.2934098</v>
       </c>
       <c r="N60">
-        <v>2.795179066666667</v>
+        <v>2.773256866666667</v>
       </c>
       <c r="O60">
-        <v>0.2795179066666668</v>
+        <v>0.2773256866666667</v>
       </c>
       <c r="P60">
-        <v>2.515661160000001</v>
+        <v>2.49593118</v>
       </c>
       <c r="Q60">
-        <v>5.81566116</v>
+        <v>5.79593118</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1311538855638945</v>
+        <v>0.1331428684494909</v>
       </c>
       <c r="T60">
-        <v>1.320397463884962</v>
+        <v>1.351166396552779</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.198353382814482</v>
+        <v>3.144144003444745</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08862567606429125</v>
+        <v>0.08870652019174685</v>
       </c>
       <c r="C61">
-        <v>15.51627336992299</v>
+        <v>15.15126755838577</v>
       </c>
       <c r="D61">
-        <v>31.30427336992299</v>
+        <v>31.28126755838577</v>
       </c>
       <c r="E61">
-        <v>-0.9220000000000006</v>
+        <v>-0.5800000000000018</v>
       </c>
       <c r="F61">
-        <v>20.178</v>
+        <v>20.52</v>
       </c>
       <c r="G61">
         <v>4.39</v>
@@ -6283,28 +6283,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M61">
-        <v>1.2934098</v>
+        <v>1.315332</v>
       </c>
       <c r="N61">
-        <v>2.773256866666667</v>
+        <v>2.751334666666667</v>
       </c>
       <c r="O61">
-        <v>0.2773256866666667</v>
+        <v>0.2751334666666667</v>
       </c>
       <c r="P61">
-        <v>2.49593118</v>
+        <v>2.4762012</v>
       </c>
       <c r="Q61">
-        <v>5.79593118</v>
+        <v>5.7762012</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1331428684494909</v>
+        <v>0.1352313004793671</v>
       </c>
       <c r="T61">
-        <v>1.351166396552779</v>
+        <v>1.383473775853988</v>
       </c>
       <c r="U61">
         <v>0.0641</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.144144003444745</v>
+        <v>3.091741603387332</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08870652019174685</v>
+        <v>0.08878736431920245</v>
       </c>
       <c r="C62">
-        <v>15.15126755838577</v>
+        <v>14.78629553640056</v>
       </c>
       <c r="D62">
-        <v>31.28126755838577</v>
+        <v>31.25829553640056</v>
       </c>
       <c r="E62">
-        <v>-0.5800000000000018</v>
+        <v>-0.2379999999999995</v>
       </c>
       <c r="F62">
-        <v>20.52</v>
+        <v>20.862</v>
       </c>
       <c r="G62">
         <v>4.39</v>
@@ -6365,28 +6365,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M62">
-        <v>1.315332</v>
+        <v>1.3372542</v>
       </c>
       <c r="N62">
-        <v>2.751334666666667</v>
+        <v>2.729412466666667</v>
       </c>
       <c r="O62">
-        <v>0.2751334666666667</v>
+        <v>0.2729412466666667</v>
       </c>
       <c r="P62">
-        <v>2.4762012</v>
+        <v>2.456471220000001</v>
       </c>
       <c r="Q62">
-        <v>5.7762012</v>
+        <v>5.75647122</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1352313004793671</v>
+        <v>0.1374268315876986</v>
       </c>
       <c r="T62">
-        <v>1.383473775853988</v>
+        <v>1.417437943837311</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.091741603387332</v>
+        <v>3.041057314807212</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08878736431920245</v>
+        <v>0.09322060844665803</v>
       </c>
       <c r="C63">
-        <v>14.78629553640056</v>
+        <v>13.23423521635696</v>
       </c>
       <c r="D63">
-        <v>31.25829553640056</v>
+        <v>30.04823521635696</v>
       </c>
       <c r="E63">
-        <v>-0.2379999999999995</v>
+        <v>0.1039999999999992</v>
       </c>
       <c r="F63">
-        <v>20.862</v>
+        <v>21.204</v>
       </c>
       <c r="G63">
         <v>4.39</v>
@@ -6447,45 +6447,45 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M63">
-        <v>1.3372542</v>
+        <v>1.5245676</v>
       </c>
       <c r="N63">
-        <v>2.729412466666667</v>
+        <v>2.542099066666667</v>
       </c>
       <c r="O63">
-        <v>0.2729412466666667</v>
+        <v>0.2542099066666667</v>
       </c>
       <c r="P63">
-        <v>2.456471220000001</v>
+        <v>2.287889160000001</v>
       </c>
       <c r="Q63">
-        <v>5.75647122</v>
+        <v>5.58788916</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1374268315876986</v>
+        <v>0.1397379169648895</v>
       </c>
       <c r="T63">
-        <v>1.417437943837311</v>
+        <v>1.453189699609228</v>
       </c>
       <c r="U63">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V63">
         <v>0.1</v>
       </c>
       <c r="W63">
-        <v>0.05769000000000001</v>
+        <v>0.06471</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y63">
-        <v>3.041057314807212</v>
+        <v>2.667422990405061</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09322060844665803</v>
+        <v>0.0933716525741136</v>
       </c>
       <c r="C64">
-        <v>13.23423521635696</v>
+        <v>12.85265570164514</v>
       </c>
       <c r="D64">
-        <v>30.04823521635696</v>
+        <v>30.00865570164515</v>
       </c>
       <c r="E64">
-        <v>0.1039999999999992</v>
+        <v>0.4460000000000015</v>
       </c>
       <c r="F64">
-        <v>21.204</v>
+        <v>21.546</v>
       </c>
       <c r="G64">
         <v>4.39</v>
@@ -6529,28 +6529,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M64">
-        <v>1.5245676</v>
+        <v>1.5491574</v>
       </c>
       <c r="N64">
-        <v>2.542099066666667</v>
+        <v>2.517509266666667</v>
       </c>
       <c r="O64">
-        <v>0.2542099066666667</v>
+        <v>0.2517509266666667</v>
       </c>
       <c r="P64">
-        <v>2.287889160000001</v>
+        <v>2.26575834</v>
       </c>
       <c r="Q64">
-        <v>5.58788916</v>
+        <v>5.56575834</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1397379169648895</v>
+        <v>0.1421739258759827</v>
       </c>
       <c r="T64">
-        <v>1.453189699609228</v>
+        <v>1.490873982720169</v>
       </c>
       <c r="U64">
         <v>0.07190000000000001</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.667422990405061</v>
+        <v>2.625082942938314</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.0933716525741136</v>
+        <v>0.09352269670156921</v>
       </c>
       <c r="C65">
-        <v>12.85265570164514</v>
+        <v>12.47118031799095</v>
       </c>
       <c r="D65">
-        <v>30.00865570164515</v>
+        <v>29.96918031799095</v>
       </c>
       <c r="E65">
-        <v>0.4460000000000015</v>
+        <v>0.7880000000000003</v>
       </c>
       <c r="F65">
-        <v>21.546</v>
+        <v>21.888</v>
       </c>
       <c r="G65">
         <v>4.39</v>
@@ -6611,28 +6611,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M65">
-        <v>1.5491574</v>
+        <v>1.5737472</v>
       </c>
       <c r="N65">
-        <v>2.517509266666667</v>
+        <v>2.492919466666667</v>
       </c>
       <c r="O65">
-        <v>0.2517509266666667</v>
+        <v>0.2492919466666667</v>
       </c>
       <c r="P65">
-        <v>2.26575834</v>
+        <v>2.24362752</v>
       </c>
       <c r="Q65">
-        <v>5.56575834</v>
+        <v>5.543627519999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1421739258759827</v>
+        <v>0.14474526861547</v>
       </c>
       <c r="T65">
-        <v>1.490873982720169</v>
+        <v>1.530651837115051</v>
       </c>
       <c r="U65">
         <v>0.07190000000000001</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.625082942938314</v>
+        <v>2.584066021954902</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09352269670156921</v>
+        <v>0.0936737408290248</v>
       </c>
       <c r="C66">
-        <v>12.47118031799095</v>
+        <v>12.08980865499147</v>
       </c>
       <c r="D66">
-        <v>29.96918031799095</v>
+        <v>29.92980865499147</v>
       </c>
       <c r="E66">
-        <v>0.7880000000000003</v>
+        <v>1.130000000000003</v>
       </c>
       <c r="F66">
-        <v>21.888</v>
+        <v>22.23</v>
       </c>
       <c r="G66">
         <v>4.39</v>
@@ -6693,28 +6693,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M66">
-        <v>1.5737472</v>
+        <v>1.598337</v>
       </c>
       <c r="N66">
-        <v>2.492919466666667</v>
+        <v>2.468329666666667</v>
       </c>
       <c r="O66">
-        <v>0.2492919466666667</v>
+        <v>0.2468329666666667</v>
       </c>
       <c r="P66">
-        <v>2.24362752</v>
+        <v>2.2214967</v>
       </c>
       <c r="Q66">
-        <v>5.543627519999999</v>
+        <v>5.5214967</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.14474526861547</v>
+        <v>0.1474635452257851</v>
       </c>
       <c r="T66">
-        <v>1.530651837115051</v>
+        <v>1.572702711761069</v>
       </c>
       <c r="U66">
         <v>0.07190000000000001</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.584066021954902</v>
+        <v>2.544311160078673</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.0936737408290248</v>
+        <v>0.09382478495648039</v>
       </c>
       <c r="C67">
-        <v>12.08980865499147</v>
+        <v>11.70854030439763</v>
       </c>
       <c r="D67">
-        <v>29.92980865499147</v>
+        <v>29.89054030439764</v>
       </c>
       <c r="E67">
-        <v>1.130000000000003</v>
+        <v>1.472000000000001</v>
       </c>
       <c r="F67">
-        <v>22.23</v>
+        <v>22.572</v>
       </c>
       <c r="G67">
         <v>4.39</v>
@@ -6775,28 +6775,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M67">
-        <v>1.598337</v>
+        <v>1.6229268</v>
       </c>
       <c r="N67">
-        <v>2.468329666666667</v>
+        <v>2.443739866666667</v>
       </c>
       <c r="O67">
-        <v>0.2468329666666667</v>
+        <v>0.2443739866666667</v>
       </c>
       <c r="P67">
-        <v>2.2214967</v>
+        <v>2.199365880000001</v>
       </c>
       <c r="Q67">
-        <v>5.5214967</v>
+        <v>5.499365880000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1474635452257851</v>
+        <v>0.1503417204602364</v>
       </c>
       <c r="T67">
-        <v>1.572702711761069</v>
+        <v>1.617227167268617</v>
       </c>
       <c r="U67">
         <v>0.07190000000000001</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.544311160078673</v>
+        <v>2.505760990986572</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09382478495648039</v>
+        <v>0.09632752908393596</v>
       </c>
       <c r="C68">
-        <v>11.70854030439763</v>
+        <v>10.73055823708259</v>
       </c>
       <c r="D68">
-        <v>29.89054030439764</v>
+        <v>29.25455823708259</v>
       </c>
       <c r="E68">
-        <v>1.472000000000001</v>
+        <v>1.814000000000004</v>
       </c>
       <c r="F68">
-        <v>22.572</v>
+        <v>22.91400000000001</v>
       </c>
       <c r="G68">
         <v>4.39</v>
@@ -6857,45 +6857,45 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M68">
-        <v>1.6229268</v>
+        <v>1.7368812</v>
       </c>
       <c r="N68">
-        <v>2.443739866666667</v>
+        <v>2.329785466666667</v>
       </c>
       <c r="O68">
-        <v>0.2443739866666667</v>
+        <v>0.2329785466666667</v>
       </c>
       <c r="P68">
-        <v>2.199365880000001</v>
+        <v>2.09680692</v>
       </c>
       <c r="Q68">
-        <v>5.499365880000001</v>
+        <v>5.39680692</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1503417204602364</v>
+        <v>0.1533943305573817</v>
       </c>
       <c r="T68">
-        <v>1.617227167268617</v>
+        <v>1.664450074625108</v>
       </c>
       <c r="U68">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V68">
         <v>0.1</v>
       </c>
       <c r="W68">
-        <v>0.06471</v>
+        <v>0.06822</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y68">
-        <v>2.505760990986572</v>
+        <v>2.341361439496648</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09632752908393596</v>
+        <v>0.09651367321139157</v>
       </c>
       <c r="C69">
-        <v>10.73055823708259</v>
+        <v>10.34233601612996</v>
       </c>
       <c r="D69">
-        <v>29.25455823708259</v>
+        <v>29.20833601612997</v>
       </c>
       <c r="E69">
-        <v>1.814000000000004</v>
+        <v>2.156000000000002</v>
       </c>
       <c r="F69">
-        <v>22.91400000000001</v>
+        <v>23.256</v>
       </c>
       <c r="G69">
         <v>4.39</v>
@@ -6939,28 +6939,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M69">
-        <v>1.7368812</v>
+        <v>1.762804800000001</v>
       </c>
       <c r="N69">
-        <v>2.329785466666667</v>
+        <v>2.303861866666667</v>
       </c>
       <c r="O69">
-        <v>0.2329785466666667</v>
+        <v>0.2303861866666667</v>
       </c>
       <c r="P69">
-        <v>2.09680692</v>
+        <v>2.07347568</v>
       </c>
       <c r="Q69">
-        <v>5.39680692</v>
+        <v>5.37347568</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1533943305573817</v>
+        <v>0.1566377287855986</v>
       </c>
       <c r="T69">
-        <v>1.664450074625108</v>
+        <v>1.71462441369138</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.341361439496648</v>
+        <v>2.306929653621697</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09651367321139157</v>
+        <v>0.09669981733884715</v>
       </c>
       <c r="C70">
-        <v>10.34233601612996</v>
+        <v>9.954259627040958</v>
       </c>
       <c r="D70">
-        <v>29.20833601612997</v>
+        <v>29.16225962704096</v>
       </c>
       <c r="E70">
-        <v>2.156000000000002</v>
+        <v>2.498000000000001</v>
       </c>
       <c r="F70">
-        <v>23.256</v>
+        <v>23.598</v>
       </c>
       <c r="G70">
         <v>4.39</v>
@@ -7021,28 +7021,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M70">
-        <v>1.762804800000001</v>
+        <v>1.7887284</v>
       </c>
       <c r="N70">
-        <v>2.303861866666667</v>
+        <v>2.277938266666667</v>
       </c>
       <c r="O70">
-        <v>0.2303861866666667</v>
+        <v>0.2277938266666667</v>
       </c>
       <c r="P70">
-        <v>2.07347568</v>
+        <v>2.05014444</v>
       </c>
       <c r="Q70">
-        <v>5.37347568</v>
+        <v>5.35014444</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1566377287855986</v>
+        <v>0.1600903785124102</v>
       </c>
       <c r="T70">
-        <v>1.71462441369138</v>
+        <v>1.768035806890959</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.306929653621697</v>
+        <v>2.273495890525731</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09669981733884715</v>
+        <v>0.09688596146630274</v>
       </c>
       <c r="C71">
-        <v>9.954259627040958</v>
+        <v>9.566328380749695</v>
       </c>
       <c r="D71">
-        <v>29.16225962704096</v>
+        <v>29.1163283807497</v>
       </c>
       <c r="E71">
-        <v>2.498000000000001</v>
+        <v>2.840000000000003</v>
       </c>
       <c r="F71">
-        <v>23.598</v>
+        <v>23.94</v>
       </c>
       <c r="G71">
         <v>4.39</v>
@@ -7103,28 +7103,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M71">
-        <v>1.7887284</v>
+        <v>1.814652000000001</v>
       </c>
       <c r="N71">
-        <v>2.277938266666667</v>
+        <v>2.252014666666667</v>
       </c>
       <c r="O71">
-        <v>0.2277938266666667</v>
+        <v>0.2252014666666667</v>
       </c>
       <c r="P71">
-        <v>2.05014444</v>
+        <v>2.0268132</v>
       </c>
       <c r="Q71">
-        <v>5.35014444</v>
+        <v>5.3268132</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1600903785124102</v>
+        <v>0.1637732048876758</v>
       </c>
       <c r="T71">
-        <v>1.768035806890959</v>
+        <v>1.825007959637176</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.273495890525731</v>
+        <v>2.241017377803935</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09688596146630274</v>
+        <v>0.09707210559375833</v>
       </c>
       <c r="C72">
-        <v>9.566328380749695</v>
+        <v>9.178541592524667</v>
       </c>
       <c r="D72">
-        <v>29.1163283807497</v>
+        <v>29.07054159252467</v>
       </c>
       <c r="E72">
-        <v>2.840000000000003</v>
+        <v>3.182000000000002</v>
       </c>
       <c r="F72">
-        <v>23.94</v>
+        <v>24.282</v>
       </c>
       <c r="G72">
         <v>4.39</v>
@@ -7185,28 +7185,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M72">
-        <v>1.814652000000001</v>
+        <v>1.8405756</v>
       </c>
       <c r="N72">
-        <v>2.252014666666667</v>
+        <v>2.226091066666667</v>
       </c>
       <c r="O72">
-        <v>0.2252014666666667</v>
+        <v>0.2226091066666667</v>
       </c>
       <c r="P72">
-        <v>2.0268132</v>
+        <v>2.00348196</v>
       </c>
       <c r="Q72">
-        <v>5.3268132</v>
+        <v>5.30348196</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1637732048876758</v>
+        <v>0.1677100192888218</v>
       </c>
       <c r="T72">
-        <v>1.825007959637176</v>
+        <v>1.885909226365892</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.241017377803935</v>
+        <v>2.209453752764443</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09707210559375833</v>
+        <v>0.09725824972121391</v>
       </c>
       <c r="C73">
-        <v>9.17854159252467</v>
+        <v>8.790898581934691</v>
       </c>
       <c r="D73">
-        <v>29.07054159252467</v>
+        <v>29.02489858193469</v>
       </c>
       <c r="E73">
-        <v>3.181999999999999</v>
+        <v>3.524000000000001</v>
       </c>
       <c r="F73">
-        <v>24.282</v>
+        <v>24.624</v>
       </c>
       <c r="G73">
         <v>4.39</v>
@@ -7267,28 +7267,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M73">
-        <v>1.8405756</v>
+        <v>1.8664992</v>
       </c>
       <c r="N73">
-        <v>2.226091066666667</v>
+        <v>2.200167466666667</v>
       </c>
       <c r="O73">
-        <v>0.2226091066666667</v>
+        <v>0.2200167466666667</v>
       </c>
       <c r="P73">
-        <v>2.00348196</v>
+        <v>1.98015072</v>
       </c>
       <c r="Q73">
-        <v>5.30348196</v>
+        <v>5.28015072</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1677100192888218</v>
+        <v>0.1719280347186211</v>
       </c>
       <c r="T73">
-        <v>1.885909226365892</v>
+        <v>1.95116058357523</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.209453752764444</v>
+        <v>2.178766895087159</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09725824972121391</v>
+        <v>0.09744439384866949</v>
       </c>
       <c r="C74">
-        <v>8.790898581934691</v>
+        <v>8.403398672815193</v>
       </c>
       <c r="D74">
-        <v>29.02489858193469</v>
+        <v>28.97939867281519</v>
       </c>
       <c r="E74">
-        <v>3.524000000000001</v>
+        <v>3.866</v>
       </c>
       <c r="F74">
-        <v>24.624</v>
+        <v>24.966</v>
       </c>
       <c r="G74">
         <v>4.39</v>
@@ -7349,28 +7349,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M74">
-        <v>1.8664992</v>
+        <v>1.8924228</v>
       </c>
       <c r="N74">
-        <v>2.200167466666667</v>
+        <v>2.174243866666667</v>
       </c>
       <c r="O74">
-        <v>0.2200167466666667</v>
+        <v>0.2174243866666667</v>
       </c>
       <c r="P74">
-        <v>1.98015072</v>
+        <v>1.95681948</v>
       </c>
       <c r="Q74">
-        <v>5.28015072</v>
+        <v>5.25681948</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1719280347186211</v>
+        <v>0.1764584957358129</v>
       </c>
       <c r="T74">
-        <v>1.95116058357523</v>
+        <v>2.021245374651926</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.178766895087159</v>
+        <v>2.14892077323665</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09744439384866949</v>
+        <v>0.09763053797612509</v>
       </c>
       <c r="C75">
-        <v>8.403398672815193</v>
+        <v>8.016041193234823</v>
       </c>
       <c r="D75">
-        <v>28.97939867281519</v>
+        <v>28.93404119323483</v>
       </c>
       <c r="E75">
-        <v>3.866</v>
+        <v>4.208000000000002</v>
       </c>
       <c r="F75">
-        <v>24.966</v>
+        <v>25.308</v>
       </c>
       <c r="G75">
         <v>4.39</v>
@@ -7431,28 +7431,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M75">
-        <v>1.8924228</v>
+        <v>1.9183464</v>
       </c>
       <c r="N75">
-        <v>2.174243866666667</v>
+        <v>2.148320266666667</v>
       </c>
       <c r="O75">
-        <v>0.2174243866666667</v>
+        <v>0.2148320266666667</v>
       </c>
       <c r="P75">
-        <v>1.95681948</v>
+        <v>1.93348824</v>
       </c>
       <c r="Q75">
-        <v>5.25681948</v>
+        <v>5.23348824</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1764584957358129</v>
+        <v>0.1813374537543272</v>
       </c>
       <c r="T75">
-        <v>2.021245374651926</v>
+        <v>2.096721303503753</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.14892077323665</v>
+        <v>2.119881303328047</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09763053797612509</v>
+        <v>0.09781668210358069</v>
       </c>
       <c r="C76">
-        <v>8.016041193234823</v>
+        <v>7.628825475462424</v>
       </c>
       <c r="D76">
-        <v>28.93404119323483</v>
+        <v>28.88882547546243</v>
       </c>
       <c r="E76">
-        <v>4.208000000000002</v>
+        <v>4.550000000000001</v>
       </c>
       <c r="F76">
-        <v>25.308</v>
+        <v>25.65</v>
       </c>
       <c r="G76">
         <v>4.39</v>
@@ -7513,28 +7513,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M76">
-        <v>1.9183464</v>
+        <v>1.94427</v>
       </c>
       <c r="N76">
-        <v>2.148320266666667</v>
+        <v>2.122396666666667</v>
       </c>
       <c r="O76">
-        <v>0.2148320266666667</v>
+        <v>0.2122396666666667</v>
       </c>
       <c r="P76">
-        <v>1.93348824</v>
+        <v>1.910157</v>
       </c>
       <c r="Q76">
-        <v>5.23348824</v>
+        <v>5.210157000000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1813374537543272</v>
+        <v>0.1866067284143227</v>
       </c>
       <c r="T76">
-        <v>2.096721303503753</v>
+        <v>2.178235306663726</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.119881303328047</v>
+        <v>2.091616219283673</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09781668210358069</v>
+        <v>0.09800282623103627</v>
       </c>
       <c r="C77">
-        <v>7.628825475462424</v>
+        <v>7.241750855934189</v>
       </c>
       <c r="D77">
-        <v>28.88882547546243</v>
+        <v>28.84375085593419</v>
       </c>
       <c r="E77">
-        <v>4.550000000000001</v>
+        <v>4.891999999999999</v>
       </c>
       <c r="F77">
-        <v>25.65</v>
+        <v>25.992</v>
       </c>
       <c r="G77">
         <v>4.39</v>
@@ -7595,28 +7595,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M77">
-        <v>1.94427</v>
+        <v>1.9701936</v>
       </c>
       <c r="N77">
-        <v>2.122396666666667</v>
+        <v>2.096473066666667</v>
       </c>
       <c r="O77">
-        <v>0.2122396666666667</v>
+        <v>0.2096473066666668</v>
       </c>
       <c r="P77">
-        <v>1.910157</v>
+        <v>1.886825760000001</v>
       </c>
       <c r="Q77">
-        <v>5.210157000000001</v>
+        <v>5.186825760000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1866067284143227</v>
+        <v>0.1923151092959845</v>
       </c>
       <c r="T77">
-        <v>2.178235306663726</v>
+        <v>2.266542143420364</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.091616219283673</v>
+        <v>2.064094953240467</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09800282623103627</v>
+        <v>0.09818897035849186</v>
       </c>
       <c r="C78">
-        <v>7.241750855934189</v>
+        <v>6.854816675221251</v>
       </c>
       <c r="D78">
-        <v>28.84375085593419</v>
+        <v>28.79881667522125</v>
       </c>
       <c r="E78">
-        <v>4.891999999999999</v>
+        <v>5.234000000000002</v>
       </c>
       <c r="F78">
-        <v>25.992</v>
+        <v>26.334</v>
       </c>
       <c r="G78">
         <v>4.39</v>
@@ -7677,28 +7677,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M78">
-        <v>1.9701936</v>
+        <v>1.9961172</v>
       </c>
       <c r="N78">
-        <v>2.096473066666667</v>
+        <v>2.070549466666667</v>
       </c>
       <c r="O78">
-        <v>0.2096473066666668</v>
+        <v>0.2070549466666667</v>
       </c>
       <c r="P78">
-        <v>1.886825760000001</v>
+        <v>1.86349452</v>
       </c>
       <c r="Q78">
-        <v>5.186825760000001</v>
+        <v>5.16349452</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1923151092959845</v>
+        <v>0.1985198711238776</v>
       </c>
       <c r="T78">
-        <v>2.266542143420364</v>
+        <v>2.362527835547144</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.064094953240467</v>
+        <v>2.037288525276304</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09818897035849186</v>
+        <v>0.09837511448594745</v>
       </c>
       <c r="C79">
-        <v>6.854816675221251</v>
+        <v>6.468022277997505</v>
       </c>
       <c r="D79">
-        <v>28.79881667522125</v>
+        <v>28.75402227799751</v>
       </c>
       <c r="E79">
-        <v>5.234000000000002</v>
+        <v>5.576000000000001</v>
       </c>
       <c r="F79">
-        <v>26.334</v>
+        <v>26.676</v>
       </c>
       <c r="G79">
         <v>4.39</v>
@@ -7759,28 +7759,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M79">
-        <v>1.9961172</v>
+        <v>2.022040800000001</v>
       </c>
       <c r="N79">
-        <v>2.070549466666667</v>
+        <v>2.044625866666667</v>
       </c>
       <c r="O79">
-        <v>0.2070549466666667</v>
+        <v>0.2044625866666667</v>
       </c>
       <c r="P79">
-        <v>1.86349452</v>
+        <v>1.84016328</v>
       </c>
       <c r="Q79">
-        <v>5.16349452</v>
+        <v>5.140163279999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1985198711238776</v>
+        <v>0.205288702208852</v>
       </c>
       <c r="T79">
-        <v>2.362527835547144</v>
+        <v>2.46723949968545</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.037288525276304</v>
+        <v>2.011169441618916</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09837511448594745</v>
+        <v>0.108657458613403</v>
       </c>
       <c r="C80">
-        <v>6.468022277997505</v>
+        <v>3.850962495312636</v>
       </c>
       <c r="D80">
-        <v>28.75402227799751</v>
+        <v>26.47896249531264</v>
       </c>
       <c r="E80">
-        <v>5.576000000000001</v>
+        <v>5.918000000000003</v>
       </c>
       <c r="F80">
-        <v>26.676</v>
+        <v>27.018</v>
       </c>
       <c r="G80">
         <v>4.39</v>
@@ -7841,45 +7841,45 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M80">
-        <v>2.022040800000001</v>
+        <v>2.43162</v>
       </c>
       <c r="N80">
-        <v>2.044625866666667</v>
+        <v>1.635046666666667</v>
       </c>
       <c r="O80">
-        <v>0.2044625866666667</v>
+        <v>0.1635046666666667</v>
       </c>
       <c r="P80">
-        <v>1.84016328</v>
+        <v>1.471542</v>
       </c>
       <c r="Q80">
-        <v>5.140163279999999</v>
+        <v>4.771542</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.205288702208852</v>
+        <v>0.2127021838733478</v>
       </c>
       <c r="T80">
-        <v>2.46723949968545</v>
+        <v>2.581923703265498</v>
       </c>
       <c r="U80">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V80">
         <v>0.1</v>
       </c>
       <c r="W80">
-        <v>0.06822</v>
+        <v>0.081</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y80">
-        <v>2.011169441618916</v>
+        <v>1.672410436937789</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.108657458613403</v>
+        <v>0.1089714027408586</v>
       </c>
       <c r="C81">
-        <v>3.850962495312636</v>
+        <v>3.44514973746173</v>
       </c>
       <c r="D81">
-        <v>26.47896249531264</v>
+        <v>26.41514973746173</v>
       </c>
       <c r="E81">
-        <v>5.918000000000003</v>
+        <v>6.260000000000002</v>
       </c>
       <c r="F81">
-        <v>27.018</v>
+        <v>27.36</v>
       </c>
       <c r="G81">
         <v>4.39</v>
@@ -7923,28 +7923,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M81">
-        <v>2.43162</v>
+        <v>2.4624</v>
       </c>
       <c r="N81">
-        <v>1.635046666666667</v>
+        <v>1.604266666666667</v>
       </c>
       <c r="O81">
-        <v>0.1635046666666667</v>
+        <v>0.1604266666666667</v>
       </c>
       <c r="P81">
-        <v>1.471542</v>
+        <v>1.44384</v>
       </c>
       <c r="Q81">
-        <v>4.771542</v>
+        <v>4.743840000000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2127021838733478</v>
+        <v>0.2208570137042931</v>
       </c>
       <c r="T81">
-        <v>2.581923703265498</v>
+        <v>2.708076327203552</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.672410436937789</v>
+        <v>1.651505306476067</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1089714027408586</v>
+        <v>0.1092853468683142</v>
       </c>
       <c r="C82">
-        <v>3.44514973746173</v>
+        <v>3.039643810228618</v>
       </c>
       <c r="D82">
-        <v>26.41514973746173</v>
+        <v>26.35164381022862</v>
       </c>
       <c r="E82">
-        <v>6.260000000000002</v>
+        <v>6.602000000000004</v>
       </c>
       <c r="F82">
-        <v>27.36</v>
+        <v>27.70200000000001</v>
       </c>
       <c r="G82">
         <v>4.39</v>
@@ -8005,28 +8005,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M82">
-        <v>2.4624</v>
+        <v>2.49318</v>
       </c>
       <c r="N82">
-        <v>1.604266666666667</v>
+        <v>1.573486666666667</v>
       </c>
       <c r="O82">
-        <v>0.1604266666666667</v>
+        <v>0.1573486666666667</v>
       </c>
       <c r="P82">
-        <v>1.44384</v>
+        <v>1.416138</v>
       </c>
       <c r="Q82">
-        <v>4.743840000000001</v>
+        <v>4.716138</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2208570137042931</v>
+        <v>0.229870246675338</v>
       </c>
       <c r="T82">
-        <v>2.708076327203552</v>
+        <v>2.847508174714033</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.651505306476067</v>
+        <v>1.631116352075128</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1092853468683142</v>
+        <v>0.1095992909957698</v>
       </c>
       <c r="C83">
-        <v>3.039643810228618</v>
+        <v>2.634442505922358</v>
       </c>
       <c r="D83">
-        <v>26.35164381022862</v>
+        <v>26.28844250592236</v>
       </c>
       <c r="E83">
-        <v>6.602000000000004</v>
+        <v>6.944000000000003</v>
       </c>
       <c r="F83">
-        <v>27.70200000000001</v>
+        <v>28.044</v>
       </c>
       <c r="G83">
         <v>4.39</v>
@@ -8087,28 +8087,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M83">
-        <v>2.49318</v>
+        <v>2.52396</v>
       </c>
       <c r="N83">
-        <v>1.573486666666667</v>
+        <v>1.542706666666667</v>
       </c>
       <c r="O83">
-        <v>0.1573486666666667</v>
+        <v>0.1542706666666667</v>
       </c>
       <c r="P83">
-        <v>1.416138</v>
+        <v>1.388436</v>
       </c>
       <c r="Q83">
-        <v>4.716138</v>
+        <v>4.688436</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.229870246675338</v>
+        <v>0.2398849499764989</v>
       </c>
       <c r="T83">
-        <v>2.847508174714033</v>
+        <v>3.002432449725678</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.631116352075128</v>
+        <v>1.611224689244943</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1095992909957698</v>
+        <v>0.1099132351232254</v>
       </c>
       <c r="C84">
-        <v>2.634442505922358</v>
+        <v>2.229543637980843</v>
       </c>
       <c r="D84">
-        <v>26.28844250592236</v>
+        <v>26.22554363798085</v>
       </c>
       <c r="E84">
-        <v>6.944000000000003</v>
+        <v>7.286000000000005</v>
       </c>
       <c r="F84">
-        <v>28.044</v>
+        <v>28.38600000000001</v>
       </c>
       <c r="G84">
         <v>4.39</v>
@@ -8169,28 +8169,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M84">
-        <v>2.52396</v>
+        <v>2.554740000000001</v>
       </c>
       <c r="N84">
-        <v>1.542706666666667</v>
+        <v>1.511926666666667</v>
       </c>
       <c r="O84">
-        <v>0.1542706666666667</v>
+        <v>0.1511926666666667</v>
       </c>
       <c r="P84">
-        <v>1.388436</v>
+        <v>1.360734</v>
       </c>
       <c r="Q84">
-        <v>4.688436</v>
+        <v>4.660734</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2398849499764989</v>
+        <v>0.2510778536660317</v>
       </c>
       <c r="T84">
-        <v>3.002432449725678</v>
+        <v>3.17558311003281</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.611224689244943</v>
+        <v>1.59181234359139</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1099132351232254</v>
+        <v>0.110227179250681</v>
       </c>
       <c r="C85">
-        <v>2.229543637980843</v>
+        <v>1.82494504071871</v>
       </c>
       <c r="D85">
-        <v>26.22554363798085</v>
+        <v>26.16294504071871</v>
       </c>
       <c r="E85">
-        <v>7.286000000000005</v>
+        <v>7.628000000000004</v>
       </c>
       <c r="F85">
-        <v>28.38600000000001</v>
+        <v>28.72800000000001</v>
       </c>
       <c r="G85">
         <v>4.39</v>
@@ -8251,28 +8251,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M85">
-        <v>2.554740000000001</v>
+        <v>2.58552</v>
       </c>
       <c r="N85">
-        <v>1.511926666666667</v>
+        <v>1.481146666666667</v>
       </c>
       <c r="O85">
-        <v>0.1511926666666667</v>
+        <v>0.1481146666666667</v>
       </c>
       <c r="P85">
-        <v>1.360734</v>
+        <v>1.333032</v>
       </c>
       <c r="Q85">
-        <v>4.660734</v>
+        <v>4.633032</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2510778536660317</v>
+        <v>0.2636698703167562</v>
       </c>
       <c r="T85">
-        <v>3.17558311003281</v>
+        <v>3.370377602878335</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.59181234359139</v>
+        <v>1.572862196643873</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.110227179250681</v>
+        <v>0.1105411233781366</v>
       </c>
       <c r="C86">
-        <v>1.824945040718713</v>
+        <v>1.420644569078704</v>
       </c>
       <c r="D86">
-        <v>26.16294504071871</v>
+        <v>26.1006445690787</v>
       </c>
       <c r="E86">
-        <v>7.628</v>
+        <v>7.969999999999999</v>
       </c>
       <c r="F86">
-        <v>28.728</v>
+        <v>29.07</v>
       </c>
       <c r="G86">
         <v>4.39</v>
@@ -8333,28 +8333,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M86">
-        <v>2.58552</v>
+        <v>2.6163</v>
       </c>
       <c r="N86">
-        <v>1.481146666666667</v>
+        <v>1.450366666666667</v>
       </c>
       <c r="O86">
-        <v>0.1481146666666667</v>
+        <v>0.1450366666666668</v>
       </c>
       <c r="P86">
-        <v>1.333032</v>
+        <v>1.305330000000001</v>
       </c>
       <c r="Q86">
-        <v>4.633032</v>
+        <v>4.60533</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.263669870316756</v>
+        <v>0.2779408225209103</v>
       </c>
       <c r="T86">
-        <v>3.370377602878333</v>
+        <v>3.591144694769927</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.572862196643873</v>
+        <v>1.554357935506887</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1105411233781366</v>
+        <v>0.1108550675055922</v>
       </c>
       <c r="C87">
-        <v>1.420644569078704</v>
+        <v>1.016640098386684</v>
       </c>
       <c r="D87">
-        <v>26.1006445690787</v>
+        <v>26.03864009838669</v>
       </c>
       <c r="E87">
-        <v>7.969999999999999</v>
+        <v>8.312000000000001</v>
       </c>
       <c r="F87">
-        <v>29.07</v>
+        <v>29.412</v>
       </c>
       <c r="G87">
         <v>4.39</v>
@@ -8415,28 +8415,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M87">
-        <v>2.6163</v>
+        <v>2.64708</v>
       </c>
       <c r="N87">
-        <v>1.450366666666667</v>
+        <v>1.419586666666667</v>
       </c>
       <c r="O87">
-        <v>0.1450366666666668</v>
+        <v>0.1419586666666667</v>
       </c>
       <c r="P87">
-        <v>1.305330000000001</v>
+        <v>1.277628</v>
       </c>
       <c r="Q87">
-        <v>4.60533</v>
+        <v>4.577628</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2779408225209103</v>
+        <v>0.294250482182801</v>
       </c>
       <c r="T87">
-        <v>3.591144694769927</v>
+        <v>3.843449942646034</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.554357935506887</v>
+        <v>1.536284006024248</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1108550675055922</v>
+        <v>0.1111690116330477</v>
       </c>
       <c r="C88">
-        <v>1.016640098386684</v>
+        <v>0.6129295241101254</v>
       </c>
       <c r="D88">
-        <v>26.03864009838669</v>
+        <v>25.97692952411013</v>
       </c>
       <c r="E88">
-        <v>8.312000000000001</v>
+        <v>8.654</v>
       </c>
       <c r="F88">
-        <v>29.412</v>
+        <v>29.754</v>
       </c>
       <c r="G88">
         <v>4.39</v>
@@ -8497,28 +8497,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M88">
-        <v>2.64708</v>
+        <v>2.67786</v>
       </c>
       <c r="N88">
-        <v>1.419586666666667</v>
+        <v>1.388806666666667</v>
       </c>
       <c r="O88">
-        <v>0.1419586666666667</v>
+        <v>0.1388806666666667</v>
       </c>
       <c r="P88">
-        <v>1.277628</v>
+        <v>1.249926000000001</v>
       </c>
       <c r="Q88">
-        <v>4.577628</v>
+        <v>4.549926000000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.294250482182801</v>
+        <v>0.3130693202542134</v>
       </c>
       <c r="T88">
-        <v>3.843449942646034</v>
+        <v>4.134571382503081</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.536284006024248</v>
+        <v>1.518625569173395</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1111690116330477</v>
+        <v>0.1114829557605033</v>
       </c>
       <c r="C89">
-        <v>0.6129295241101254</v>
+        <v>0.2095107616199492</v>
       </c>
       <c r="D89">
-        <v>25.97692952411013</v>
+        <v>25.91551076161995</v>
       </c>
       <c r="E89">
-        <v>8.654</v>
+        <v>8.996000000000002</v>
       </c>
       <c r="F89">
-        <v>29.754</v>
+        <v>30.096</v>
       </c>
       <c r="G89">
         <v>4.39</v>
@@ -8579,28 +8579,28 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M89">
-        <v>2.67786</v>
+        <v>2.70864</v>
       </c>
       <c r="N89">
-        <v>1.388806666666667</v>
+        <v>1.358026666666667</v>
       </c>
       <c r="O89">
-        <v>0.1388806666666667</v>
+        <v>0.1358026666666667</v>
       </c>
       <c r="P89">
-        <v>1.249926000000001</v>
+        <v>1.222224</v>
       </c>
       <c r="Q89">
-        <v>4.549926000000001</v>
+        <v>4.522224</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3130693202542134</v>
+        <v>0.3350246313375277</v>
       </c>
       <c r="T89">
-        <v>4.134571382503081</v>
+        <v>4.474213062336303</v>
       </c>
       <c r="U89">
         <v>0.09</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.518625569173395</v>
+        <v>1.501368460432788</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1114829557605033</v>
+        <v>0.158772498757146</v>
       </c>
       <c r="C90">
-        <v>0.2095107616199492</v>
+        <v>-6.938299987884196</v>
       </c>
       <c r="D90">
-        <v>25.91551076161995</v>
+        <v>19.10970001211581</v>
       </c>
       <c r="E90">
-        <v>8.996000000000002</v>
+        <v>9.338000000000001</v>
       </c>
       <c r="F90">
-        <v>30.096</v>
+        <v>30.438</v>
       </c>
       <c r="G90">
         <v>4.39</v>
@@ -8661,45 +8661,45 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M90">
-        <v>2.70864</v>
+        <v>4.468298400000001</v>
       </c>
       <c r="N90">
-        <v>1.358026666666667</v>
+        <v>-0.4016317333333337</v>
       </c>
       <c r="O90">
-        <v>0.1358026666666667</v>
+        <v>-0.04016317333333337</v>
       </c>
       <c r="P90">
-        <v>1.222224</v>
+        <v>-0.3614685600000003</v>
       </c>
       <c r="Q90">
-        <v>4.522224</v>
+        <v>2.938531439999999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3350246313375277</v>
+        <v>0.3637394269433969</v>
       </c>
       <c r="T90">
-        <v>4.474213062336303</v>
+        <v>4.918421817959762</v>
       </c>
       <c r="U90">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.1</v>
+        <v>0.09101152838554083</v>
       </c>
       <c r="W90">
-        <v>0.081</v>
+        <v>0.1334395076330026</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y90">
-        <v>1.501368460432788</v>
+        <v>0.9101152838554082</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.158772498757146</v>
+        <v>0.159782498757146</v>
       </c>
       <c r="C91">
-        <v>-6.938299987884196</v>
+        <v>-7.386886222748309</v>
       </c>
       <c r="D91">
-        <v>19.10970001211581</v>
+        <v>19.00311377725169</v>
       </c>
       <c r="E91">
-        <v>9.338000000000001</v>
+        <v>9.680000000000003</v>
       </c>
       <c r="F91">
-        <v>30.438</v>
+        <v>30.78</v>
       </c>
       <c r="G91">
         <v>4.39</v>
@@ -8743,37 +8743,37 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M91">
-        <v>4.468298400000001</v>
+        <v>4.518504000000001</v>
       </c>
       <c r="N91">
-        <v>-0.4016317333333337</v>
+        <v>-0.4518373333333336</v>
       </c>
       <c r="O91">
-        <v>-0.04016317333333337</v>
+        <v>-0.04518373333333336</v>
       </c>
       <c r="P91">
-        <v>-0.3614685600000003</v>
+        <v>-0.4066536000000003</v>
       </c>
       <c r="Q91">
-        <v>2.938531439999999</v>
+        <v>2.8933464</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3637394269433969</v>
+        <v>0.3955333696377366</v>
       </c>
       <c r="T91">
-        <v>4.918421817959762</v>
+        <v>5.410263999755738</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.09101152838554083</v>
+        <v>0.09000028918125703</v>
       </c>
       <c r="W91">
-        <v>0.1334395076330026</v>
+        <v>0.1335879575481915</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.9101152838554082</v>
+        <v>0.9000028918125704</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.159782498757146</v>
+        <v>0.160792498757146</v>
       </c>
       <c r="C92">
-        <v>-7.386886222748309</v>
+        <v>-7.834290062084321</v>
       </c>
       <c r="D92">
-        <v>19.00311377725169</v>
+        <v>18.89770993791568</v>
       </c>
       <c r="E92">
-        <v>9.680000000000003</v>
+        <v>10.022</v>
       </c>
       <c r="F92">
-        <v>30.78</v>
+        <v>31.122</v>
       </c>
       <c r="G92">
         <v>4.39</v>
@@ -8825,37 +8825,37 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M92">
-        <v>4.518504000000001</v>
+        <v>4.568709600000001</v>
       </c>
       <c r="N92">
-        <v>-0.4518373333333336</v>
+        <v>-0.5020429333333336</v>
       </c>
       <c r="O92">
-        <v>-0.04518373333333336</v>
+        <v>-0.05020429333333336</v>
       </c>
       <c r="P92">
-        <v>-0.4066536000000003</v>
+        <v>-0.4518386400000002</v>
       </c>
       <c r="Q92">
-        <v>2.8933464</v>
+        <v>2.84816136</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3955333696377366</v>
+        <v>0.4343926329308185</v>
       </c>
       <c r="T92">
-        <v>5.410263999755738</v>
+        <v>6.011404444173043</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.09000028918125703</v>
+        <v>0.08901127501443004</v>
       </c>
       <c r="W92">
-        <v>0.1335879575481915</v>
+        <v>0.1337331448278817</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.9000028918125704</v>
+        <v>0.8901127501443004</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.160792498757146</v>
+        <v>0.161802498757146</v>
       </c>
       <c r="C93">
-        <v>-7.834290062084321</v>
+        <v>-8.280531072406628</v>
       </c>
       <c r="D93">
-        <v>18.89770993791568</v>
+        <v>18.79346892759338</v>
       </c>
       <c r="E93">
-        <v>10.022</v>
+        <v>10.364</v>
       </c>
       <c r="F93">
-        <v>31.122</v>
+        <v>31.46400000000001</v>
       </c>
       <c r="G93">
         <v>4.39</v>
@@ -8907,37 +8907,37 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M93">
-        <v>4.568709600000001</v>
+        <v>4.618915200000001</v>
       </c>
       <c r="N93">
-        <v>-0.5020429333333336</v>
+        <v>-0.5522485333333336</v>
       </c>
       <c r="O93">
-        <v>-0.05020429333333336</v>
+        <v>-0.05522485333333336</v>
       </c>
       <c r="P93">
-        <v>-0.4518386400000002</v>
+        <v>-0.4970236800000002</v>
       </c>
       <c r="Q93">
-        <v>2.84816136</v>
+        <v>2.80297632</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4343926329308185</v>
+        <v>0.4829667120471708</v>
       </c>
       <c r="T93">
-        <v>6.011404444173043</v>
+        <v>6.762829999694675</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.08901127501443004</v>
+        <v>0.08804376115557755</v>
       </c>
       <c r="W93">
-        <v>0.1337331448278817</v>
+        <v>0.1338751758623612</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8901127501443004</v>
+        <v>0.8804376115557754</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.161802498757146</v>
+        <v>0.162812498757146</v>
       </c>
       <c r="C94">
-        <v>-8.280531072406628</v>
+        <v>-8.725628390877226</v>
       </c>
       <c r="D94">
-        <v>18.79346892759338</v>
+        <v>18.69037160912278</v>
       </c>
       <c r="E94">
-        <v>10.364</v>
+        <v>10.706</v>
       </c>
       <c r="F94">
-        <v>31.46400000000001</v>
+        <v>31.806</v>
       </c>
       <c r="G94">
         <v>4.39</v>
@@ -8989,37 +8989,37 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M94">
-        <v>4.618915200000001</v>
+        <v>4.669120800000001</v>
       </c>
       <c r="N94">
-        <v>-0.5522485333333336</v>
+        <v>-0.6024541333333335</v>
       </c>
       <c r="O94">
-        <v>-0.05522485333333336</v>
+        <v>-0.06024541333333336</v>
       </c>
       <c r="P94">
-        <v>-0.4970236800000002</v>
+        <v>-0.5422087200000002</v>
       </c>
       <c r="Q94">
-        <v>2.80297632</v>
+        <v>2.75779128</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4829667120471708</v>
+        <v>0.545419099482481</v>
       </c>
       <c r="T94">
-        <v>6.762829999694675</v>
+        <v>7.72894857107963</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.08804376115557755</v>
+        <v>0.08709705404637778</v>
       </c>
       <c r="W94">
-        <v>0.1338751758623612</v>
+        <v>0.1340141524659917</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8804376115557754</v>
+        <v>0.8709705404637778</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.162812498757146</v>
+        <v>0.163822498757146</v>
       </c>
       <c r="C95">
-        <v>-8.725628390877226</v>
+        <v>-9.169600737018204</v>
       </c>
       <c r="D95">
-        <v>18.69037160912278</v>
+        <v>18.5883992629818</v>
       </c>
       <c r="E95">
-        <v>10.706</v>
+        <v>11.048</v>
       </c>
       <c r="F95">
-        <v>31.806</v>
+        <v>32.148</v>
       </c>
       <c r="G95">
         <v>4.39</v>
@@ -9071,37 +9071,37 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M95">
-        <v>4.669120800000001</v>
+        <v>4.719326400000001</v>
       </c>
       <c r="N95">
-        <v>-0.6024541333333335</v>
+        <v>-0.6526597333333335</v>
       </c>
       <c r="O95">
-        <v>-0.06024541333333336</v>
+        <v>-0.06526597333333335</v>
       </c>
       <c r="P95">
-        <v>-0.5422087200000002</v>
+        <v>-0.5873937600000001</v>
       </c>
       <c r="Q95">
-        <v>2.75779128</v>
+        <v>2.71260624</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.545419099482481</v>
+        <v>0.628688949396228</v>
       </c>
       <c r="T95">
-        <v>7.72894857107963</v>
+        <v>9.01710666625957</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.08709705404637778</v>
+        <v>0.08617048964162909</v>
       </c>
       <c r="W95">
-        <v>0.1340141524659917</v>
+        <v>0.1341501721206089</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8709705404637778</v>
+        <v>0.8617048964162908</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.163822498757146</v>
+        <v>0.164832498757146</v>
       </c>
       <c r="C96">
-        <v>-9.169600737018204</v>
+        <v>-9.612466424042871</v>
       </c>
       <c r="D96">
-        <v>18.5883992629818</v>
+        <v>18.48753357595713</v>
       </c>
       <c r="E96">
-        <v>11.048</v>
+        <v>11.39</v>
       </c>
       <c r="F96">
-        <v>32.148</v>
+        <v>32.49</v>
       </c>
       <c r="G96">
         <v>4.39</v>
@@ -9153,37 +9153,37 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M96">
-        <v>4.719326400000001</v>
+        <v>4.769532000000001</v>
       </c>
       <c r="N96">
-        <v>-0.6526597333333335</v>
+        <v>-0.7028653333333335</v>
       </c>
       <c r="O96">
-        <v>-0.06526597333333335</v>
+        <v>-0.07028653333333335</v>
       </c>
       <c r="P96">
-        <v>-0.5873937600000001</v>
+        <v>-0.6325788000000001</v>
       </c>
       <c r="Q96">
-        <v>2.71260624</v>
+        <v>2.6674212</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.628688949396228</v>
+        <v>0.7452667392754739</v>
       </c>
       <c r="T96">
-        <v>9.01710666625957</v>
+        <v>10.82052799951149</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.08617048964162909</v>
+        <v>0.08526343185592772</v>
       </c>
       <c r="W96">
-        <v>0.1341501721206089</v>
+        <v>0.1342833282035498</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8617048964162908</v>
+        <v>0.8526343185592773</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.164832498757146</v>
+        <v>0.165842498757146</v>
       </c>
       <c r="C97">
-        <v>-9.612466424042871</v>
+        <v>-10.05424336981996</v>
       </c>
       <c r="D97">
-        <v>18.48753357595713</v>
+        <v>18.38775663018005</v>
       </c>
       <c r="E97">
-        <v>11.39</v>
+        <v>11.73200000000001</v>
       </c>
       <c r="F97">
-        <v>32.49</v>
+        <v>32.83200000000001</v>
       </c>
       <c r="G97">
         <v>4.39</v>
@@ -9235,37 +9235,37 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M97">
-        <v>4.769532000000001</v>
+        <v>4.819737600000002</v>
       </c>
       <c r="N97">
-        <v>-0.7028653333333335</v>
+        <v>-0.7530709333333343</v>
       </c>
       <c r="O97">
-        <v>-0.07028653333333335</v>
+        <v>-0.07530709333333344</v>
       </c>
       <c r="P97">
-        <v>-0.6325788000000001</v>
+        <v>-0.6777638400000009</v>
       </c>
       <c r="Q97">
-        <v>2.6674212</v>
+        <v>2.622236159999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7452667392754739</v>
+        <v>0.9201334240943428</v>
       </c>
       <c r="T97">
-        <v>10.82052799951149</v>
+        <v>13.52565999938937</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.08526343185592772</v>
+        <v>0.08437527110742847</v>
       </c>
       <c r="W97">
-        <v>0.1342833282035498</v>
+        <v>0.1344137102014295</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8526343185592773</v>
+        <v>0.8437527110742846</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.165842498757146</v>
+        <v>0.166852498757146</v>
       </c>
       <c r="C98">
-        <v>-10.05424336981995</v>
+        <v>-10.49494910748472</v>
       </c>
       <c r="D98">
-        <v>18.38775663018005</v>
+        <v>18.28905089251528</v>
       </c>
       <c r="E98">
-        <v>11.732</v>
+        <v>12.074</v>
       </c>
       <c r="F98">
-        <v>32.832</v>
+        <v>33.174</v>
       </c>
       <c r="G98">
         <v>4.39</v>
@@ -9317,37 +9317,37 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M98">
-        <v>4.819737600000001</v>
+        <v>4.869943200000001</v>
       </c>
       <c r="N98">
-        <v>-0.7530709333333334</v>
+        <v>-0.8032765333333334</v>
       </c>
       <c r="O98">
-        <v>-0.07530709333333335</v>
+        <v>-0.08032765333333335</v>
       </c>
       <c r="P98">
-        <v>-0.6777638400000001</v>
+        <v>-0.72294888</v>
       </c>
       <c r="Q98">
-        <v>2.62223616</v>
+        <v>2.57705112</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9201334240943405</v>
+        <v>1.211577898792454</v>
       </c>
       <c r="T98">
-        <v>13.52565999938933</v>
+        <v>18.03421333251911</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.08437527110742848</v>
+        <v>0.0835054229516818</v>
       </c>
       <c r="W98">
-        <v>0.1344137102014295</v>
+        <v>0.1345414039106931</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8437527110742847</v>
+        <v>0.835054229516818</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.166852498757146</v>
+        <v>0.167862498757146</v>
       </c>
       <c r="C99">
-        <v>-10.49494910748472</v>
+        <v>-10.93460079571006</v>
       </c>
       <c r="D99">
-        <v>18.28905089251528</v>
+        <v>18.19139920428994</v>
       </c>
       <c r="E99">
-        <v>12.074</v>
+        <v>12.416</v>
       </c>
       <c r="F99">
-        <v>33.174</v>
+        <v>33.51600000000001</v>
       </c>
       <c r="G99">
         <v>4.39</v>
@@ -9399,37 +9399,37 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M99">
-        <v>4.869943200000001</v>
+        <v>4.920148800000002</v>
       </c>
       <c r="N99">
-        <v>-0.8032765333333334</v>
+        <v>-0.8534821333333342</v>
       </c>
       <c r="O99">
-        <v>-0.08032765333333335</v>
+        <v>-0.08534821333333342</v>
       </c>
       <c r="P99">
-        <v>-0.72294888</v>
+        <v>-0.7681339200000008</v>
       </c>
       <c r="Q99">
-        <v>2.57705112</v>
+        <v>2.531866079999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.211577898792454</v>
+        <v>1.794466848188681</v>
       </c>
       <c r="T99">
-        <v>18.03421333251911</v>
+        <v>27.05131999877866</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.0835054229516818</v>
+        <v>0.08265332679911361</v>
       </c>
       <c r="W99">
-        <v>0.1345414039106931</v>
+        <v>0.1346664916258901</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.835054229516818</v>
+        <v>0.8265332679911359</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.167862498757146</v>
+        <v>0.168872498757146</v>
       </c>
       <c r="C100">
-        <v>-10.93460079571006</v>
+        <v>-11.37321522865034</v>
       </c>
       <c r="D100">
-        <v>18.19139920428994</v>
+        <v>18.09478477134967</v>
       </c>
       <c r="E100">
-        <v>12.416</v>
+        <v>12.758</v>
       </c>
       <c r="F100">
-        <v>33.51600000000001</v>
+        <v>33.858</v>
       </c>
       <c r="G100">
         <v>4.39</v>
@@ -9481,37 +9481,37 @@
         <v>4.066666666666667</v>
       </c>
       <c r="M100">
-        <v>4.920148800000002</v>
+        <v>4.970354400000002</v>
       </c>
       <c r="N100">
-        <v>-0.8534821333333342</v>
+        <v>-0.9036877333333342</v>
       </c>
       <c r="O100">
-        <v>-0.08534821333333342</v>
+        <v>-0.09036877333333343</v>
       </c>
       <c r="P100">
-        <v>-0.7681339200000008</v>
+        <v>-0.8133189600000008</v>
       </c>
       <c r="Q100">
-        <v>2.531866079999999</v>
+        <v>2.486681039999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.794466848188681</v>
+        <v>3.543133696377362</v>
       </c>
       <c r="T100">
-        <v>27.05131999877866</v>
+        <v>54.10263999755733</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.08265332679911361</v>
+        <v>0.08181844471023367</v>
       </c>
       <c r="W100">
-        <v>0.1346664916258901</v>
+        <v>0.1347890523165377</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8265332679911359</v>
+        <v>0.8181844471023366</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.168872498757146</v>
-      </c>
-      <c r="C101">
-        <v>-11.37321522865034</v>
-      </c>
-      <c r="D101">
-        <v>18.09478477134967</v>
-      </c>
-      <c r="E101">
-        <v>12.758</v>
-      </c>
-      <c r="F101">
-        <v>33.858</v>
-      </c>
-      <c r="G101">
-        <v>4.39</v>
-      </c>
-      <c r="H101">
-        <v>13.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>7.366666666666667</v>
-      </c>
-      <c r="K101">
-        <v>3.3</v>
-      </c>
-      <c r="L101">
-        <v>4.066666666666667</v>
-      </c>
-      <c r="M101">
-        <v>4.970354400000002</v>
-      </c>
-      <c r="N101">
-        <v>-0.9036877333333342</v>
-      </c>
-      <c r="O101">
-        <v>-0.09036877333333343</v>
-      </c>
-      <c r="P101">
-        <v>-0.8133189600000008</v>
-      </c>
-      <c r="Q101">
-        <v>2.486681039999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.543133696377362</v>
-      </c>
-      <c r="T101">
-        <v>54.10263999755733</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.08181844471023367</v>
-      </c>
-      <c r="W101">
-        <v>0.1347890523165377</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8181844471023366</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
